--- a/models/49sectors_exiobase/transport.xlsx
+++ b/models/49sectors_exiobase/transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\01.Feina_CREAF\06.Git_Repos\pymedeas2_vensim\models_for_pymedeas2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E8E760-A076-42FE-A7AA-3CF07FB04337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7820224-B765-4270-AFC7-173BEA032C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="28800" windowHeight="14415" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28050" windowHeight="13995" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -52,6 +52,8 @@
     <definedName name="H_4wheels_elec" localSheetId="1">World!$B$50</definedName>
     <definedName name="H_4wheels_hyb" localSheetId="2">Europe!#REF!</definedName>
     <definedName name="H_4wheels_hyb" localSheetId="1">World!$B$45</definedName>
+    <definedName name="historic_air_pkm_vehicles" localSheetId="2">Europe!$C$93:$AE$96</definedName>
+    <definedName name="historic_air_tkm_vehicles" localSheetId="2">Europe!$C$76:$AE$79</definedName>
     <definedName name="historic_fuel_share_households_pkm" localSheetId="2">Europe!$C$31:$AE$34</definedName>
     <definedName name="historic_fuel_share_inland_pkm" localSheetId="2">Europe!$C$27:$AE$30</definedName>
     <definedName name="historic_fuel_share_maritime_pkm" localSheetId="2">Europe!$C$39:$AE$42</definedName>
@@ -59,16 +61,18 @@
     <definedName name="historic_fuel_share_rail_tkm" localSheetId="2">Europe!$C$53:$AE$56</definedName>
     <definedName name="historic_fuel_share_road_heavy_tkm" localSheetId="2">Europe!$C$45:$AE$48</definedName>
     <definedName name="historic_fuel_share_road_light_tkm" localSheetId="2">Europe!$C$49:$AE$52</definedName>
-    <definedName name="historic_heavy_truck_vehicles" localSheetId="2">Europe!$C$66:$AE$69</definedName>
-    <definedName name="historic_household_vehicles" localSheetId="2">Europe!$C$79:$AE$82</definedName>
-    <definedName name="historic_light_truck_vehicles" localSheetId="2">Europe!$C$70:$AE$73</definedName>
+    <definedName name="historic_heavy_truck_vehicles" localSheetId="2">Europe!$C$68:$AE$71</definedName>
+    <definedName name="historic_household_vehicles" localSheetId="2">Europe!$C$97:$AE$100</definedName>
+    <definedName name="historic_light_truck_vehicles" localSheetId="2">Europe!$C$80:$AE$83</definedName>
     <definedName name="historic_pkm" localSheetId="2">Europe!$C$19:$AE$19</definedName>
     <definedName name="historic_pkm_GDP" localSheetId="3">Catalonia!$B$18:$V$18</definedName>
     <definedName name="historic_pkm_GDP" localSheetId="1">World!$B$15:$V$15</definedName>
-    <definedName name="historic_share_batteries_bus" localSheetId="2">Europe!$C$95:$L$99</definedName>
-    <definedName name="historic_share_batteries_ev" localSheetId="2">Europe!$C$90:$L$94</definedName>
-    <definedName name="historic_share_batteries_heavy_trucks" localSheetId="2">Europe!$C$105:$L$109</definedName>
-    <definedName name="historic_share_batteries_trucks" localSheetId="2">Europe!$C$100:$L$104</definedName>
+    <definedName name="historic_rail_pkm_vehicles" localSheetId="2">Europe!$C$89:$AE$92</definedName>
+    <definedName name="historic_rail_tkm_vehicles" localSheetId="2">Europe!$C$72:$AE$75</definedName>
+    <definedName name="historic_share_batteries_bus" localSheetId="2">Europe!$C$113:$L$117</definedName>
+    <definedName name="historic_share_batteries_ev" localSheetId="2">Europe!$C$108:$L$112</definedName>
+    <definedName name="historic_share_batteries_heavy_trucks" localSheetId="2">Europe!$C$123:$L$127</definedName>
+    <definedName name="historic_share_batteries_trucks" localSheetId="2">Europe!$C$118:$L$122</definedName>
     <definedName name="historic_tkm" localSheetId="2">Europe!$C$12:$AE$12</definedName>
     <definedName name="historic_tkm_GDP" localSheetId="3">Catalonia!$B$12:$V$12</definedName>
     <definedName name="historic_tkm_GDP" localSheetId="1">World!$B$10:$V$10</definedName>
@@ -80,12 +84,12 @@
     <definedName name="initial_economy_transport_tkm" localSheetId="2">Europe!#REF!</definedName>
     <definedName name="initial_economy_transport_tkm" localSheetId="1">World!$B$113</definedName>
     <definedName name="initial_ei_households_transport" localSheetId="3">Catalonia!$B$123:$B$127</definedName>
-    <definedName name="initial_ei_households_transport" localSheetId="2">Europe!$B$114:$B$118</definedName>
+    <definedName name="initial_ei_households_transport" localSheetId="2">Europe!$B$132:$B$136</definedName>
     <definedName name="initial_ei_households_transport" localSheetId="1">World!$B$128:$B$132</definedName>
     <definedName name="initial_energy_intensity_households_transport" localSheetId="3">Catalonia!$B$123:$B$126</definedName>
     <definedName name="initial_energy_intensity_households_transport" localSheetId="1">World!$B$121:$B$125</definedName>
     <definedName name="initial_fuel_share_air_pkm" localSheetId="3">Catalonia!$D$35:$D$38</definedName>
-    <definedName name="initial_fuel_share_air_pkm" localSheetId="2">Europe!$D$61:$D$85</definedName>
+    <definedName name="initial_fuel_share_air_pkm" localSheetId="2">Europe!$D$61:$D$103</definedName>
     <definedName name="initial_fuel_share_air_pkm" localSheetId="1">World!$D$31:$D$34</definedName>
     <definedName name="initial_fuel_share_air_tkm" localSheetId="3">Catalonia!$C$35:$C$38</definedName>
     <definedName name="initial_fuel_share_air_tkm" localSheetId="2">Europe!$C$58:$C$61</definedName>
@@ -116,11 +120,14 @@
     <definedName name="initial_pkm__commercial_inland" localSheetId="1">World!$B$73</definedName>
     <definedName name="initial_pkm_gdp_2015" localSheetId="2">Europe!$W$16</definedName>
     <definedName name="initial_pkm_households" localSheetId="3">Catalonia!$B$51</definedName>
-    <definedName name="initial_pkm_vehicles_com" localSheetId="2">Europe!$C$75:$AE$78</definedName>
+    <definedName name="initial_pkm_vehicles_com" localSheetId="2">Europe!$C$85:$AE$88</definedName>
     <definedName name="initial_pkm_vehicles_com" localSheetId="1">World!$B$71</definedName>
+    <definedName name="initial_rail_kms" localSheetId="2">Europe!$AE$63</definedName>
     <definedName name="initial_share_comercial_pkm" localSheetId="2">Europe!$AE$20</definedName>
     <definedName name="initial_share_pkm_2015" localSheetId="2">Europe!$V$17:$V$20</definedName>
     <definedName name="initial_share_private_pkm" localSheetId="2">Europe!$AE$21</definedName>
+    <definedName name="initial_share_rail_pkm" localSheetId="2">Europe!$AE$22</definedName>
+    <definedName name="initial_share_rail_tkm" localSheetId="2">Europe!$C$15</definedName>
     <definedName name="initial_share_road_heavy_tkm" localSheetId="2">Europe!$AE$13</definedName>
     <definedName name="initial_share_road_light_tkm" localSheetId="2">Europe!$AE$14</definedName>
     <definedName name="initial_share_road_tkm" localSheetId="2">Europe!$AE$13</definedName>
@@ -129,6 +136,8 @@
     <definedName name="initial_vehicles_inland" localSheetId="2">Europe!#REF!</definedName>
     <definedName name="initial_vehicles_inland" localSheetId="1">World!$B$58:$B$70</definedName>
     <definedName name="initial_Xt_inland" localSheetId="3">Catalonia!$B$116</definedName>
+    <definedName name="lifetime_pkm" localSheetId="0">Global!$B$33:$F$33</definedName>
+    <definedName name="lifetime_tkm" localSheetId="0">Global!$B$49:$F$49</definedName>
     <definedName name="liq_2w" localSheetId="3">Catalonia!$B$96</definedName>
     <definedName name="liq_4w" localSheetId="3">Catalonia!$B$92</definedName>
     <definedName name="liq_4w" localSheetId="1">World!$B$89</definedName>
@@ -167,7 +176,7 @@
     <definedName name="tkm_gdp_slope" localSheetId="3">Catalonia!$B$5</definedName>
     <definedName name="tkm_gdp_slope" localSheetId="1">World!$B$5</definedName>
     <definedName name="tkm_initial" localSheetId="2">Europe!$AE$12</definedName>
-    <definedName name="year_hist_batteries" localSheetId="2">Europe!$C$89:$L$89</definedName>
+    <definedName name="year_hist_batteries" localSheetId="2">Europe!$C$107:$L$107</definedName>
     <definedName name="year0_pkm" localSheetId="2">Europe!$C$8</definedName>
     <definedName name="year0_tkm" localSheetId="2">Europe!$B$8</definedName>
   </definedNames>
@@ -1269,7 +1278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="207">
   <si>
     <t>TECHNOLOGICAL CONSTANTS</t>
   </si>
@@ -1881,6 +1890,15 @@
   </si>
   <si>
     <t>Xt(0)_pkm</t>
+  </si>
+  <si>
+    <t>lifetime (Years)</t>
+  </si>
+  <si>
+    <t>lifetime(Years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historic rail kms </t>
   </si>
 </sst>
 </file>
@@ -2730,7 +2748,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2987,6 +3005,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3014,6 +3035,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3022,12 +3049,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3442,13 +3463,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="177" t="s">
+      <c r="A9" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="177"/>
-      <c r="C9" s="177"/>
-      <c r="D9" s="177"/>
-      <c r="E9" s="177"/>
+      <c r="B9" s="180"/>
+      <c r="C9" s="180"/>
+      <c r="D9" s="180"/>
+      <c r="E9" s="180"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
@@ -3534,13 +3555,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="178" t="s">
+      <c r="A15" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="178"/>
-      <c r="C15" s="178"/>
-      <c r="D15" s="178"/>
-      <c r="E15" s="178"/>
+      <c r="B15" s="181"/>
+      <c r="C15" s="181"/>
+      <c r="D15" s="181"/>
+      <c r="E15" s="181"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
@@ -3643,14 +3664,14 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="178" t="s">
+      <c r="A22" s="181" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="178"/>
-      <c r="C22" s="178"/>
-      <c r="D22" s="178"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="178"/>
+      <c r="B22" s="181"/>
+      <c r="C22" s="181"/>
+      <c r="D22" s="181"/>
+      <c r="E22" s="181"/>
+      <c r="F22" s="181"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="24"/>
@@ -3751,14 +3772,14 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="176" t="s">
+      <c r="A28" s="179" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="176"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="176"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
+      <c r="B28" s="179"/>
+      <c r="C28" s="179"/>
+      <c r="D28" s="179"/>
+      <c r="E28" s="179"/>
+      <c r="F28" s="179"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="40" t="s">
@@ -3840,15 +3861,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="162" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="164">
+        <v>15</v>
+      </c>
+      <c r="C33" s="164">
+        <v>18</v>
+      </c>
+      <c r="D33" s="164">
+        <v>35</v>
+      </c>
+      <c r="E33" s="164">
+        <v>30</v>
+      </c>
+      <c r="F33" s="164">
+        <v>25</v>
+      </c>
+    </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="178" t="s">
+      <c r="A38" s="181" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="178"/>
-      <c r="C38" s="178"/>
-      <c r="D38" s="178"/>
-      <c r="E38" s="178"/>
-      <c r="F38" s="178"/>
+      <c r="B38" s="181"/>
+      <c r="C38" s="181"/>
+      <c r="D38" s="181"/>
+      <c r="E38" s="181"/>
+      <c r="F38" s="181"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="40"/>
@@ -3949,14 +3990,14 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="176" t="s">
+      <c r="A44" s="179" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="176"/>
-      <c r="C44" s="176"/>
-      <c r="D44" s="176"/>
-      <c r="E44" s="176"/>
-      <c r="F44" s="176"/>
+      <c r="B44" s="179"/>
+      <c r="C44" s="179"/>
+      <c r="D44" s="179"/>
+      <c r="E44" s="179"/>
+      <c r="F44" s="179"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
@@ -4036,6 +4077,26 @@
       </c>
       <c r="F48" s="19">
         <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="163" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" s="164">
+        <v>15</v>
+      </c>
+      <c r="C49" s="164">
+        <v>14</v>
+      </c>
+      <c r="D49" s="164">
+        <v>35</v>
+      </c>
+      <c r="E49" s="164">
+        <v>30</v>
+      </c>
+      <c r="F49" s="164">
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4452,30 +4513,30 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="181" t="s">
+      <c r="A8" s="184" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
-      <c r="E8" s="181"/>
-      <c r="F8" s="181"/>
-      <c r="G8" s="181"/>
-      <c r="H8" s="181"/>
-      <c r="I8" s="181"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="181"/>
-      <c r="M8" s="181"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="181"/>
-      <c r="P8" s="181"/>
-      <c r="Q8" s="181"/>
-      <c r="R8" s="181"/>
-      <c r="S8" s="181"/>
-      <c r="T8" s="181"/>
-      <c r="U8" s="181"/>
-      <c r="V8" s="181"/>
+      <c r="B8" s="184"/>
+      <c r="C8" s="184"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="184"/>
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="184"/>
+      <c r="Q8" s="184"/>
+      <c r="R8" s="184"/>
+      <c r="S8" s="184"/>
+      <c r="T8" s="184"/>
+      <c r="U8" s="184"/>
+      <c r="V8" s="184"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="63" t="s">
@@ -4878,30 +4939,30 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="181" t="s">
+      <c r="A14" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="181"/>
-      <c r="C14" s="181"/>
-      <c r="D14" s="181"/>
-      <c r="E14" s="181"/>
-      <c r="F14" s="181"/>
-      <c r="G14" s="181"/>
-      <c r="H14" s="181"/>
-      <c r="I14" s="181"/>
-      <c r="J14" s="181"/>
-      <c r="K14" s="181"/>
-      <c r="L14" s="181"/>
-      <c r="M14" s="181"/>
-      <c r="N14" s="181"/>
-      <c r="O14" s="181"/>
-      <c r="P14" s="181"/>
-      <c r="Q14" s="181"/>
-      <c r="R14" s="181"/>
-      <c r="S14" s="181"/>
-      <c r="T14" s="181"/>
-      <c r="U14" s="181"/>
-      <c r="V14" s="181"/>
+      <c r="B14" s="184"/>
+      <c r="C14" s="184"/>
+      <c r="D14" s="184"/>
+      <c r="E14" s="184"/>
+      <c r="F14" s="184"/>
+      <c r="G14" s="184"/>
+      <c r="H14" s="184"/>
+      <c r="I14" s="184"/>
+      <c r="J14" s="184"/>
+      <c r="K14" s="184"/>
+      <c r="L14" s="184"/>
+      <c r="M14" s="184"/>
+      <c r="N14" s="184"/>
+      <c r="O14" s="184"/>
+      <c r="P14" s="184"/>
+      <c r="Q14" s="184"/>
+      <c r="R14" s="184"/>
+      <c r="S14" s="184"/>
+      <c r="T14" s="184"/>
+      <c r="U14" s="184"/>
+      <c r="V14" s="184"/>
     </row>
     <row r="15" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="63" t="s">
@@ -5260,12 +5321,12 @@
       <c r="V20" s="9"/>
     </row>
     <row r="21" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="182" t="s">
+      <c r="A21" s="185" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="182"/>
-      <c r="C21" s="182"/>
-      <c r="D21" s="182"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="185"/>
+      <c r="D21" s="185"/>
     </row>
     <row r="22" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68"/>
@@ -5278,7 +5339,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="167" t="s">
+      <c r="A23" s="170" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="64" t="s">
@@ -5293,7 +5354,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="167"/>
+      <c r="A24" s="170"/>
       <c r="B24" s="64" t="s">
         <v>13</v>
       </c>
@@ -5305,7 +5366,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="167"/>
+      <c r="A25" s="170"/>
       <c r="B25" s="64" t="s">
         <v>14</v>
       </c>
@@ -5318,7 +5379,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="167"/>
+      <c r="A26" s="170"/>
       <c r="B26" s="64" t="s">
         <v>83</v>
       </c>
@@ -5330,7 +5391,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="167" t="s">
+      <c r="A27" s="170" t="s">
         <v>18</v>
       </c>
       <c r="B27" s="64" t="s">
@@ -5344,7 +5405,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="167"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="64" t="s">
         <v>84</v>
       </c>
@@ -5356,7 +5417,7 @@
       </c>
     </row>
     <row r="29" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="167"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="64" t="s">
         <v>14</v>
       </c>
@@ -5368,7 +5429,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="167"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="64" t="s">
         <v>83</v>
       </c>
@@ -5380,7 +5441,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="167" t="s">
+      <c r="A31" s="170" t="s">
         <v>19</v>
       </c>
       <c r="B31" s="64" t="s">
@@ -5394,7 +5455,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A32" s="167"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="64" t="s">
         <v>13</v>
       </c>
@@ -5406,7 +5467,7 @@
       </c>
     </row>
     <row r="33" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A33" s="167"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="64" t="s">
         <v>14</v>
       </c>
@@ -5418,7 +5479,7 @@
       </c>
     </row>
     <row r="34" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="167"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="64" t="s">
         <v>83</v>
       </c>
@@ -5430,7 +5491,7 @@
       </c>
     </row>
     <row r="35" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="168" t="s">
+      <c r="A35" s="171" t="s">
         <v>21</v>
       </c>
       <c r="B35" s="64" t="s">
@@ -5443,7 +5504,7 @@
       </c>
     </row>
     <row r="36" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="168"/>
+      <c r="A36" s="171"/>
       <c r="B36" s="64" t="s">
         <v>13</v>
       </c>
@@ -5454,7 +5515,7 @@
       </c>
     </row>
     <row r="37" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="168"/>
+      <c r="A37" s="171"/>
       <c r="B37" s="64" t="s">
         <v>14</v>
       </c>
@@ -5465,7 +5526,7 @@
       </c>
     </row>
     <row r="38" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="168"/>
+      <c r="A38" s="171"/>
       <c r="B38" s="64" t="s">
         <v>83</v>
       </c>
@@ -5478,10 +5539,10 @@
     <row r="39" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="179" t="s">
+      <c r="A41" s="182" t="s">
         <v>85</v>
       </c>
-      <c r="B41" s="179"/>
+      <c r="B41" s="182"/>
     </row>
     <row r="42" spans="1:110" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="64" t="s">
@@ -13197,11 +13258,11 @@
       <c r="DF113" s="6"/>
     </row>
     <row r="114" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="A114" s="180" t="s">
+      <c r="A114" s="183" t="s">
         <v>144</v>
       </c>
-      <c r="B114" s="180"/>
-      <c r="C114" s="180"/>
+      <c r="B114" s="183"/>
+      <c r="C114" s="183"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -14034,7 +14095,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:DE118"/>
+  <dimension ref="A1:DE136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.7109375" customWidth="1"/>
@@ -14191,46 +14252,46 @@
       <c r="DE9" s="76"/>
     </row>
     <row r="10" spans="1:109" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="162" t="s">
+      <c r="A10" s="165" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="162"/>
-      <c r="C10" s="162"/>
-      <c r="D10" s="162"/>
-      <c r="E10" s="162"/>
-      <c r="F10" s="162"/>
-      <c r="G10" s="162"/>
-      <c r="H10" s="162"/>
-      <c r="I10" s="162"/>
-      <c r="J10" s="162"/>
-      <c r="K10" s="162"/>
-      <c r="L10" s="162"/>
-      <c r="M10" s="162"/>
-      <c r="N10" s="162"/>
-      <c r="O10" s="162"/>
-      <c r="P10" s="162"/>
-      <c r="Q10" s="162"/>
-      <c r="R10" s="162"/>
-      <c r="S10" s="162"/>
-      <c r="T10" s="162"/>
-      <c r="U10" s="162"/>
-      <c r="V10" s="162"/>
-      <c r="W10" s="162"/>
-      <c r="X10" s="162"/>
-      <c r="Y10" s="162"/>
-      <c r="Z10" s="162"/>
-      <c r="AA10" s="162"/>
-      <c r="AB10" s="162"/>
-      <c r="AC10" s="162"/>
-      <c r="AD10" s="162"/>
-      <c r="AE10" s="162"/>
+      <c r="B10" s="165"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="165"/>
+      <c r="F10" s="165"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="165"/>
+      <c r="J10" s="165"/>
+      <c r="K10" s="165"/>
+      <c r="L10" s="165"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="165"/>
+      <c r="O10" s="165"/>
+      <c r="P10" s="165"/>
+      <c r="Q10" s="165"/>
+      <c r="R10" s="165"/>
+      <c r="S10" s="165"/>
+      <c r="T10" s="165"/>
+      <c r="U10" s="165"/>
+      <c r="V10" s="165"/>
+      <c r="W10" s="165"/>
+      <c r="X10" s="165"/>
+      <c r="Y10" s="165"/>
+      <c r="Z10" s="165"/>
+      <c r="AA10" s="165"/>
+      <c r="AB10" s="165"/>
+      <c r="AC10" s="165"/>
+      <c r="AD10" s="165"/>
+      <c r="AE10" s="165"/>
       <c r="DE10" s="76"/>
     </row>
     <row r="11" spans="1:109" s="82" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="163"/>
+      <c r="B11" s="166"/>
       <c r="C11" s="63">
         <v>1995</v>
       </c>
@@ -14401,7 +14462,7 @@
       <c r="A12" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="163"/>
+      <c r="B12" s="166"/>
       <c r="C12" s="99">
         <v>1973.5655968169699</v>
       </c>
@@ -14572,7 +14633,7 @@
       <c r="A13" s="101" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="163"/>
+      <c r="B13" s="166"/>
       <c r="C13" s="99">
         <v>0.66255490525495797</v>
       </c>
@@ -14743,7 +14804,7 @@
       <c r="A14" s="101" t="s">
         <v>164</v>
       </c>
-      <c r="B14" s="163"/>
+      <c r="B14" s="166"/>
       <c r="C14" s="99">
         <v>3.4112364712135801E-2</v>
       </c>
@@ -14914,7 +14975,7 @@
       <c r="A15" s="101" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="163"/>
+      <c r="B15" s="166"/>
       <c r="C15" s="99">
         <v>0.19655832837169099</v>
       </c>
@@ -15085,7 +15146,7 @@
       <c r="A16" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="163"/>
+      <c r="B16" s="166"/>
       <c r="C16" s="99">
         <v>0.106563997639195</v>
       </c>
@@ -15256,7 +15317,7 @@
       <c r="A17" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="163"/>
+      <c r="B17" s="166"/>
       <c r="C17" s="99">
         <v>2.10404022020358E-4</v>
       </c>
@@ -15348,46 +15409,46 @@
       <c r="DE17" s="83"/>
     </row>
     <row r="18" spans="1:109" s="82" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="164" t="s">
+      <c r="A18" s="167" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="164"/>
-      <c r="C18" s="164"/>
-      <c r="D18" s="164"/>
-      <c r="E18" s="164"/>
-      <c r="F18" s="164"/>
-      <c r="G18" s="164"/>
-      <c r="H18" s="164"/>
-      <c r="I18" s="164"/>
-      <c r="J18" s="164"/>
-      <c r="K18" s="164"/>
-      <c r="L18" s="164"/>
-      <c r="M18" s="164"/>
-      <c r="N18" s="164"/>
-      <c r="O18" s="164"/>
-      <c r="P18" s="164"/>
-      <c r="Q18" s="164"/>
-      <c r="R18" s="164"/>
-      <c r="S18" s="164"/>
-      <c r="T18" s="164"/>
-      <c r="U18" s="164"/>
-      <c r="V18" s="164"/>
-      <c r="W18" s="164"/>
-      <c r="X18" s="164"/>
-      <c r="Y18" s="164"/>
-      <c r="Z18" s="164"/>
-      <c r="AA18" s="164"/>
-      <c r="AB18" s="164"/>
-      <c r="AC18" s="164"/>
-      <c r="AD18" s="164"/>
-      <c r="AE18" s="164"/>
+      <c r="B18" s="167"/>
+      <c r="C18" s="167"/>
+      <c r="D18" s="167"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="167"/>
+      <c r="J18" s="167"/>
+      <c r="K18" s="167"/>
+      <c r="L18" s="167"/>
+      <c r="M18" s="167"/>
+      <c r="N18" s="167"/>
+      <c r="O18" s="167"/>
+      <c r="P18" s="167"/>
+      <c r="Q18" s="167"/>
+      <c r="R18" s="167"/>
+      <c r="S18" s="167"/>
+      <c r="T18" s="167"/>
+      <c r="U18" s="167"/>
+      <c r="V18" s="167"/>
+      <c r="W18" s="167"/>
+      <c r="X18" s="167"/>
+      <c r="Y18" s="167"/>
+      <c r="Z18" s="167"/>
+      <c r="AA18" s="167"/>
+      <c r="AB18" s="167"/>
+      <c r="AC18" s="167"/>
+      <c r="AD18" s="167"/>
+      <c r="AE18" s="167"/>
       <c r="DE18" s="83"/>
     </row>
     <row r="19" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="101" t="s">
         <v>166</v>
       </c>
-      <c r="B19" s="165"/>
+      <c r="B19" s="168"/>
       <c r="C19" s="99">
         <v>4747.1845382983201</v>
       </c>
@@ -15558,7 +15619,7 @@
       <c r="A20" s="101" t="s">
         <v>167</v>
       </c>
-      <c r="B20" s="165"/>
+      <c r="B20" s="168"/>
       <c r="C20" s="99">
         <v>0.10467931813706501</v>
       </c>
@@ -15729,7 +15790,7 @@
       <c r="A21" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="B21" s="165"/>
+      <c r="B21" s="168"/>
       <c r="C21" s="99">
         <v>0.79236886621211799</v>
       </c>
@@ -15900,7 +15961,7 @@
       <c r="A22" s="101" t="s">
         <v>165</v>
       </c>
-      <c r="B22" s="165"/>
+      <c r="B22" s="168"/>
       <c r="C22" s="99">
         <v>8.5607191279278197E-2</v>
       </c>
@@ -16071,7 +16132,7 @@
       <c r="A23" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="165"/>
+      <c r="B23" s="168"/>
       <c r="C23" s="99">
         <v>0</v>
       </c>
@@ -16242,7 +16303,7 @@
       <c r="A24" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="165"/>
+      <c r="B24" s="168"/>
       <c r="C24" s="99">
         <v>1.7344624371538098E-2</v>
       </c>
@@ -16410,39 +16471,39 @@
       <c r="DE24" s="83"/>
     </row>
     <row r="25" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="166" t="s">
+      <c r="A25" s="169" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="166"/>
-      <c r="C25" s="166"/>
-      <c r="D25" s="166"/>
-      <c r="E25" s="166"/>
-      <c r="F25" s="166"/>
-      <c r="G25" s="166"/>
-      <c r="H25" s="166"/>
-      <c r="I25" s="166"/>
-      <c r="J25" s="166"/>
-      <c r="K25" s="166"/>
-      <c r="L25" s="166"/>
-      <c r="M25" s="166"/>
-      <c r="N25" s="166"/>
-      <c r="O25" s="166"/>
-      <c r="P25" s="166"/>
-      <c r="Q25" s="166"/>
-      <c r="R25" s="166"/>
-      <c r="S25" s="166"/>
-      <c r="T25" s="166"/>
-      <c r="U25" s="166"/>
-      <c r="V25" s="166"/>
-      <c r="W25" s="166"/>
-      <c r="X25" s="166"/>
-      <c r="Y25" s="166"/>
-      <c r="Z25" s="166"/>
-      <c r="AA25" s="166"/>
-      <c r="AB25" s="166"/>
-      <c r="AC25" s="166"/>
-      <c r="AD25" s="166"/>
-      <c r="AE25" s="166"/>
+      <c r="B25" s="169"/>
+      <c r="C25" s="169"/>
+      <c r="D25" s="169"/>
+      <c r="E25" s="169"/>
+      <c r="F25" s="169"/>
+      <c r="G25" s="169"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="169"/>
+      <c r="J25" s="169"/>
+      <c r="K25" s="169"/>
+      <c r="L25" s="169"/>
+      <c r="M25" s="169"/>
+      <c r="N25" s="169"/>
+      <c r="O25" s="169"/>
+      <c r="P25" s="169"/>
+      <c r="Q25" s="169"/>
+      <c r="R25" s="169"/>
+      <c r="S25" s="169"/>
+      <c r="T25" s="169"/>
+      <c r="U25" s="169"/>
+      <c r="V25" s="169"/>
+      <c r="W25" s="169"/>
+      <c r="X25" s="169"/>
+      <c r="Y25" s="169"/>
+      <c r="Z25" s="169"/>
+      <c r="AA25" s="169"/>
+      <c r="AB25" s="169"/>
+      <c r="AC25" s="169"/>
+      <c r="AD25" s="169"/>
+      <c r="AE25" s="169"/>
     </row>
     <row r="26" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C26" s="63">
@@ -16534,7 +16595,7 @@
       </c>
     </row>
     <row r="27" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="167" t="s">
+      <c r="A27" s="170" t="s">
         <v>16</v>
       </c>
       <c r="B27" s="64" t="s">
@@ -16629,7 +16690,7 @@
       </c>
     </row>
     <row r="28" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="167"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="64" t="s">
         <v>13</v>
       </c>
@@ -16722,7 +16783,7 @@
       </c>
     </row>
     <row r="29" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="167"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="64" t="s">
         <v>14</v>
       </c>
@@ -16815,7 +16876,7 @@
       </c>
     </row>
     <row r="30" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="167"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="64" t="s">
         <v>83</v>
       </c>
@@ -16908,7 +16969,7 @@
       </c>
     </row>
     <row r="31" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="167" t="s">
+      <c r="A31" s="170" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="64" t="s">
@@ -17003,7 +17064,7 @@
       </c>
     </row>
     <row r="32" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="167"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="64" t="s">
         <v>13</v>
       </c>
@@ -17096,7 +17157,7 @@
       </c>
     </row>
     <row r="33" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="167"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="64" t="s">
         <v>14</v>
       </c>
@@ -17189,7 +17250,7 @@
       </c>
     </row>
     <row r="34" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="167"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="64" t="s">
         <v>83</v>
       </c>
@@ -17282,7 +17343,7 @@
       </c>
     </row>
     <row r="35" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="168" t="s">
+      <c r="A35" s="171" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="64" t="s">
@@ -17377,7 +17438,7 @@
       </c>
     </row>
     <row r="36" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="168"/>
+      <c r="A36" s="171"/>
       <c r="B36" s="64" t="s">
         <v>13</v>
       </c>
@@ -17470,7 +17531,7 @@
       </c>
     </row>
     <row r="37" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="168"/>
+      <c r="A37" s="171"/>
       <c r="B37" s="64" t="s">
         <v>14</v>
       </c>
@@ -17563,7 +17624,7 @@
       </c>
     </row>
     <row r="38" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="168"/>
+      <c r="A38" s="171"/>
       <c r="B38" s="64" t="s">
         <v>83</v>
       </c>
@@ -17656,7 +17717,7 @@
       </c>
     </row>
     <row r="39" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="168" t="s">
+      <c r="A39" s="171" t="s">
         <v>18</v>
       </c>
       <c r="B39" s="64" t="s">
@@ -17751,7 +17812,7 @@
       </c>
     </row>
     <row r="40" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="168"/>
+      <c r="A40" s="171"/>
       <c r="B40" s="64" t="s">
         <v>13</v>
       </c>
@@ -17844,7 +17905,7 @@
       </c>
     </row>
     <row r="41" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="168"/>
+      <c r="A41" s="171"/>
       <c r="B41" s="64" t="s">
         <v>14</v>
       </c>
@@ -17937,7 +17998,7 @@
       </c>
     </row>
     <row r="42" spans="1:31" s="106" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="168"/>
+      <c r="A42" s="171"/>
       <c r="B42" s="64" t="s">
         <v>83</v>
       </c>
@@ -18125,42 +18186,42 @@
       </c>
     </row>
     <row r="44" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="169" t="s">
+      <c r="A44" s="172" t="s">
         <v>171</v>
       </c>
-      <c r="B44" s="169"/>
-      <c r="C44" s="169"/>
-      <c r="D44" s="169"/>
-      <c r="E44" s="169"/>
-      <c r="F44" s="169"/>
-      <c r="G44" s="169"/>
-      <c r="H44" s="169"/>
-      <c r="I44" s="169"/>
-      <c r="J44" s="169"/>
-      <c r="K44" s="169"/>
-      <c r="L44" s="169"/>
-      <c r="M44" s="169"/>
-      <c r="N44" s="169"/>
-      <c r="O44" s="169"/>
-      <c r="P44" s="169"/>
-      <c r="Q44" s="169"/>
-      <c r="R44" s="169"/>
-      <c r="S44" s="169"/>
-      <c r="T44" s="169"/>
-      <c r="U44" s="169"/>
-      <c r="V44" s="169"/>
-      <c r="W44" s="169"/>
-      <c r="X44" s="169"/>
-      <c r="Y44" s="169"/>
-      <c r="Z44" s="169"/>
-      <c r="AA44" s="169"/>
-      <c r="AB44" s="169"/>
-      <c r="AC44" s="169"/>
-      <c r="AD44" s="169"/>
-      <c r="AE44" s="169"/>
+      <c r="B44" s="172"/>
+      <c r="C44" s="172"/>
+      <c r="D44" s="172"/>
+      <c r="E44" s="172"/>
+      <c r="F44" s="172"/>
+      <c r="G44" s="172"/>
+      <c r="H44" s="172"/>
+      <c r="I44" s="172"/>
+      <c r="J44" s="172"/>
+      <c r="K44" s="172"/>
+      <c r="L44" s="172"/>
+      <c r="M44" s="172"/>
+      <c r="N44" s="172"/>
+      <c r="O44" s="172"/>
+      <c r="P44" s="172"/>
+      <c r="Q44" s="172"/>
+      <c r="R44" s="172"/>
+      <c r="S44" s="172"/>
+      <c r="T44" s="172"/>
+      <c r="U44" s="172"/>
+      <c r="V44" s="172"/>
+      <c r="W44" s="172"/>
+      <c r="X44" s="172"/>
+      <c r="Y44" s="172"/>
+      <c r="Z44" s="172"/>
+      <c r="AA44" s="172"/>
+      <c r="AB44" s="172"/>
+      <c r="AC44" s="172"/>
+      <c r="AD44" s="172"/>
+      <c r="AE44" s="172"/>
     </row>
     <row r="45" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="170" t="s">
+      <c r="A45" s="173" t="s">
         <v>172</v>
       </c>
       <c r="B45" s="64" t="s">
@@ -18255,7 +18316,7 @@
       </c>
     </row>
     <row r="46" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="170"/>
+      <c r="A46" s="173"/>
       <c r="B46" s="64" t="s">
         <v>173</v>
       </c>
@@ -18348,7 +18409,7 @@
       </c>
     </row>
     <row r="47" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="170"/>
+      <c r="A47" s="173"/>
       <c r="B47" s="64" t="s">
         <v>150</v>
       </c>
@@ -18441,7 +18502,7 @@
       </c>
     </row>
     <row r="48" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="170"/>
+      <c r="A48" s="173"/>
       <c r="B48" s="64" t="s">
         <v>174</v>
       </c>
@@ -18533,8 +18594,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="170" t="s">
+    <row r="49" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="173" t="s">
         <v>175</v>
       </c>
       <c r="B49" s="64" t="s">
@@ -18628,8 +18689,8 @@
         <v>0.99196617755663097</v>
       </c>
     </row>
-    <row r="50" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="170"/>
+    <row r="50" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="173"/>
       <c r="B50" s="64" t="s">
         <v>173</v>
       </c>
@@ -18721,8 +18782,8 @@
         <v>5.67489304298412E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="170"/>
+    <row r="51" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="173"/>
       <c r="B51" s="64" t="s">
         <v>150</v>
       </c>
@@ -18814,8 +18875,8 @@
         <v>2.3589294003847302E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="170"/>
+    <row r="52" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="173"/>
       <c r="B52" s="64" t="s">
         <v>174</v>
       </c>
@@ -18907,8 +18968,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="170" t="s">
+    <row r="53" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="173" t="s">
         <v>17</v>
       </c>
       <c r="B53" s="64" t="s">
@@ -19002,8 +19063,8 @@
         <v>0.30515229106048603</v>
       </c>
     </row>
-    <row r="54" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="170"/>
+    <row r="54" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="173"/>
       <c r="B54" s="64" t="s">
         <v>173</v>
       </c>
@@ -19095,8 +19156,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="170"/>
+    <row r="55" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="173"/>
       <c r="B55" s="64" t="s">
         <v>150</v>
       </c>
@@ -19188,8 +19249,8 @@
         <v>0.69484770893951397</v>
       </c>
     </row>
-    <row r="56" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="170"/>
+    <row r="56" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="173"/>
       <c r="B56" s="64" t="s">
         <v>174</v>
       </c>
@@ -19281,43 +19342,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A57" s="166" t="s">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A57" s="169" t="s">
         <v>176</v>
       </c>
-      <c r="B57" s="166"/>
-      <c r="C57" s="166"/>
-      <c r="D57" s="166"/>
-      <c r="E57" s="166"/>
-      <c r="F57" s="166"/>
-      <c r="G57" s="166"/>
-      <c r="H57" s="166"/>
-      <c r="I57" s="166"/>
-      <c r="J57" s="166"/>
-      <c r="K57" s="166"/>
-      <c r="L57" s="166"/>
-      <c r="M57" s="166"/>
-      <c r="N57" s="166"/>
-      <c r="O57" s="166"/>
-      <c r="P57" s="166"/>
-      <c r="Q57" s="166"/>
-      <c r="R57" s="166"/>
-      <c r="S57" s="166"/>
-      <c r="T57" s="166"/>
-      <c r="U57" s="166"/>
-      <c r="V57" s="166"/>
-      <c r="W57" s="166"/>
-      <c r="X57" s="166"/>
-      <c r="Y57" s="166"/>
-      <c r="Z57" s="166"/>
-      <c r="AA57" s="166"/>
-      <c r="AB57" s="166"/>
-      <c r="AC57" s="166"/>
-      <c r="AD57" s="166"/>
-      <c r="AE57" s="166"/>
-    </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A58" s="168" t="s">
+      <c r="B57" s="169"/>
+      <c r="C57" s="169"/>
+      <c r="D57" s="169"/>
+      <c r="E57" s="169"/>
+      <c r="F57" s="169"/>
+      <c r="G57" s="169"/>
+      <c r="H57" s="169"/>
+      <c r="I57" s="169"/>
+      <c r="J57" s="169"/>
+      <c r="K57" s="169"/>
+      <c r="L57" s="169"/>
+      <c r="M57" s="169"/>
+      <c r="N57" s="169"/>
+      <c r="O57" s="169"/>
+      <c r="P57" s="169"/>
+      <c r="Q57" s="169"/>
+      <c r="R57" s="169"/>
+      <c r="S57" s="169"/>
+      <c r="T57" s="169"/>
+      <c r="U57" s="169"/>
+      <c r="V57" s="169"/>
+      <c r="W57" s="169"/>
+      <c r="X57" s="169"/>
+      <c r="Y57" s="169"/>
+      <c r="Z57" s="169"/>
+      <c r="AA57" s="169"/>
+      <c r="AB57" s="169"/>
+      <c r="AC57" s="169"/>
+      <c r="AD57" s="169"/>
+      <c r="AE57" s="169"/>
+    </row>
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A58" s="171" t="s">
         <v>177</v>
       </c>
       <c r="B58" s="64" t="s">
@@ -19327,8 +19388,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="168"/>
+    <row r="59" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="171"/>
       <c r="B59" s="64" t="s">
         <v>13</v>
       </c>
@@ -19336,8 +19397,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A60" s="168"/>
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A60" s="171"/>
       <c r="B60" s="64" t="s">
         <v>14</v>
       </c>
@@ -19345,8 +19406,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="168"/>
+    <row r="61" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="171"/>
       <c r="B61" s="108" t="s">
         <v>83</v>
       </c>
@@ -19354,2434 +19415,4063 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A62" s="109"/>
-      <c r="C62" s="110"/>
-    </row>
-    <row r="63" spans="1:31" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A63" s="92" t="s">
-        <v>178</v>
-      </c>
-      <c r="C63" s="110"/>
-    </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A62" s="169" t="s">
+        <v>206</v>
+      </c>
+      <c r="B62" s="169"/>
+      <c r="C62" s="169"/>
+      <c r="D62" s="169"/>
+      <c r="E62" s="169"/>
+      <c r="F62" s="169"/>
+      <c r="G62" s="169"/>
+      <c r="H62" s="169"/>
+      <c r="I62" s="169"/>
+      <c r="J62" s="169"/>
+      <c r="K62" s="169"/>
+      <c r="L62" s="169"/>
+      <c r="M62" s="169"/>
+      <c r="N62" s="169"/>
+      <c r="O62" s="169"/>
+      <c r="P62" s="169"/>
+      <c r="Q62" s="169"/>
+      <c r="R62" s="169"/>
+      <c r="S62" s="169"/>
+      <c r="T62" s="169"/>
+      <c r="U62" s="169"/>
+      <c r="V62" s="169"/>
+      <c r="W62" s="169"/>
+      <c r="X62" s="169"/>
+      <c r="Y62" s="169"/>
+      <c r="Z62" s="169"/>
+      <c r="AA62" s="169"/>
+      <c r="AB62" s="169"/>
+      <c r="AC62" s="169"/>
+      <c r="AD62" s="169"/>
+      <c r="AE62" s="169"/>
+    </row>
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A63" s="109"/>
+      <c r="C63" s="110">
+        <v>212745.5</v>
+      </c>
+      <c r="D63">
+        <v>211354.5</v>
+      </c>
+      <c r="E63">
+        <v>208665.2</v>
+      </c>
+      <c r="F63">
+        <v>207481</v>
+      </c>
+      <c r="G63">
+        <v>206447</v>
+      </c>
+      <c r="H63">
+        <v>204726.34</v>
+      </c>
+      <c r="I63">
+        <v>202956.2</v>
+      </c>
+      <c r="J63">
+        <v>202371.9</v>
+      </c>
+      <c r="K63">
+        <v>207158.7</v>
+      </c>
+      <c r="L63">
+        <v>205802.5</v>
+      </c>
+      <c r="M63">
+        <v>204051.3</v>
+      </c>
+      <c r="N63">
+        <v>204716.27</v>
+      </c>
+      <c r="O63">
+        <v>204659.77</v>
+      </c>
+      <c r="P63">
+        <v>204682.07</v>
+      </c>
+      <c r="Q63">
+        <v>204392.27</v>
+      </c>
+      <c r="R63">
+        <v>205137.67</v>
+      </c>
+      <c r="S63">
+        <v>205019.13</v>
+      </c>
+      <c r="T63">
+        <v>204989</v>
+      </c>
+      <c r="U63">
+        <v>203925.50099999999</v>
+      </c>
+      <c r="V63">
+        <v>202059.36499999999</v>
+      </c>
+      <c r="W63">
+        <v>201703.70199999999</v>
+      </c>
+      <c r="X63">
+        <v>202685.44200000001</v>
+      </c>
+      <c r="Y63">
+        <v>203178.503</v>
+      </c>
+      <c r="Z63">
+        <v>202170.05799999999</v>
+      </c>
+      <c r="AA63">
+        <v>202974.587</v>
+      </c>
+      <c r="AB63">
+        <v>202656.18299999999</v>
+      </c>
+      <c r="AC63">
+        <v>202652.55600000001</v>
+      </c>
+      <c r="AD63">
+        <v>202327.67499999999</v>
+      </c>
+      <c r="AE63">
+        <v>201329.783</v>
+      </c>
+      <c r="AF63">
+        <v>201314.277</v>
+      </c>
+    </row>
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="109"/>
       <c r="C64" s="110"/>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A65" s="171" t="s">
+    <row r="65" spans="1:31" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A65" s="92" t="s">
+        <v>178</v>
+      </c>
+      <c r="C65" s="110"/>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A66" s="109"/>
+      <c r="C66" s="110"/>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A67" s="176" t="s">
         <v>179</v>
       </c>
-      <c r="B65" s="171"/>
-      <c r="C65" s="171"/>
-      <c r="D65" s="171"/>
-      <c r="E65" s="171"/>
-      <c r="F65" s="171"/>
-      <c r="G65" s="171"/>
-      <c r="H65" s="171"/>
-      <c r="I65" s="171"/>
-      <c r="J65" s="171"/>
-      <c r="K65" s="171"/>
-      <c r="L65" s="171"/>
-      <c r="M65" s="171"/>
-      <c r="N65" s="171"/>
-      <c r="O65" s="171"/>
-      <c r="P65" s="171"/>
-      <c r="Q65" s="171"/>
-      <c r="R65" s="171"/>
-      <c r="S65" s="171"/>
-      <c r="T65" s="171"/>
-      <c r="U65" s="171"/>
-      <c r="V65" s="171"/>
-      <c r="W65" s="171"/>
-      <c r="X65" s="171"/>
-      <c r="Y65" s="171"/>
-      <c r="Z65" s="171"/>
-      <c r="AA65" s="171"/>
-      <c r="AB65" s="171"/>
-      <c r="AC65" s="171"/>
-      <c r="AD65" s="171"/>
-      <c r="AE65" s="171"/>
-    </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A66" s="172" t="s">
+      <c r="B67" s="176"/>
+      <c r="C67" s="176"/>
+      <c r="D67" s="176"/>
+      <c r="E67" s="176"/>
+      <c r="F67" s="176"/>
+      <c r="G67" s="176"/>
+      <c r="H67" s="176"/>
+      <c r="I67" s="176"/>
+      <c r="J67" s="176"/>
+      <c r="K67" s="176"/>
+      <c r="L67" s="176"/>
+      <c r="M67" s="176"/>
+      <c r="N67" s="176"/>
+      <c r="O67" s="176"/>
+      <c r="P67" s="176"/>
+      <c r="Q67" s="176"/>
+      <c r="R67" s="176"/>
+      <c r="S67" s="176"/>
+      <c r="T67" s="176"/>
+      <c r="U67" s="176"/>
+      <c r="V67" s="176"/>
+      <c r="W67" s="176"/>
+      <c r="X67" s="176"/>
+      <c r="Y67" s="176"/>
+      <c r="Z67" s="176"/>
+      <c r="AA67" s="176"/>
+      <c r="AB67" s="176"/>
+      <c r="AC67" s="176"/>
+      <c r="AD67" s="176"/>
+      <c r="AE67" s="176"/>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A68" s="177" t="s">
         <v>172</v>
       </c>
-      <c r="B66" s="111" t="s">
+      <c r="B68" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="112">
+      <c r="C68" s="112">
         <v>4558818</v>
       </c>
-      <c r="D66" s="112">
+      <c r="D68" s="112">
         <v>4558818</v>
       </c>
-      <c r="E66" s="112">
+      <c r="E68" s="112">
         <v>4558818</v>
       </c>
-      <c r="F66" s="112">
+      <c r="F68" s="112">
         <v>4558818</v>
       </c>
-      <c r="G66" s="112">
+      <c r="G68" s="112">
         <v>4558818</v>
       </c>
-      <c r="H66" s="113">
+      <c r="H68" s="113">
         <v>4558818</v>
       </c>
-      <c r="I66" s="113">
+      <c r="I68" s="113">
         <v>4686389</v>
       </c>
-      <c r="J66" s="113">
+      <c r="J68" s="113">
         <v>4778166</v>
       </c>
-      <c r="K66" s="113">
+      <c r="K68" s="113">
         <v>4821627</v>
       </c>
-      <c r="L66" s="113">
+      <c r="L68" s="113">
         <v>4810887</v>
       </c>
-      <c r="M66" s="113">
+      <c r="M68" s="113">
         <v>4859466</v>
       </c>
-      <c r="N66" s="113">
+      <c r="N68" s="113">
         <v>4986293</v>
       </c>
-      <c r="O66" s="113">
+      <c r="O68" s="113">
         <v>4996372</v>
       </c>
-      <c r="P66" s="113">
+      <c r="P68" s="113">
         <v>5085013</v>
       </c>
-      <c r="Q66" s="113">
+      <c r="Q68" s="113">
         <v>5030816</v>
       </c>
-      <c r="R66" s="113">
+      <c r="R68" s="113">
         <v>5025317</v>
       </c>
-      <c r="S66" s="113">
+      <c r="S68" s="113">
         <v>5035683</v>
       </c>
-      <c r="T66" s="113">
+      <c r="T68" s="113">
         <v>4941991</v>
       </c>
-      <c r="U66" s="113">
+      <c r="U68" s="113">
         <v>4720453</v>
       </c>
-      <c r="V66" s="113">
+      <c r="V68" s="113">
         <v>4773182</v>
       </c>
-      <c r="W66" s="113">
+      <c r="W68" s="113">
         <v>4799062</v>
       </c>
-      <c r="X66" s="113">
+      <c r="X68" s="113">
         <v>4792440</v>
       </c>
-      <c r="Y66" s="113">
+      <c r="Y68" s="113">
         <v>4841582</v>
       </c>
-      <c r="Z66" s="113">
+      <c r="Z68" s="113">
         <v>4977180</v>
       </c>
-      <c r="AA66" s="113">
+      <c r="AA68" s="113">
         <v>5092648</v>
       </c>
-      <c r="AB66" s="113">
+      <c r="AB68" s="113">
         <v>5105252</v>
       </c>
-      <c r="AC66" s="113">
+      <c r="AC68" s="113">
         <v>5170979</v>
       </c>
-      <c r="AD66" s="113">
+      <c r="AD68" s="113">
         <v>5256238</v>
       </c>
-      <c r="AE66" s="114">
+      <c r="AE68" s="114">
         <v>5390897</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A67" s="172"/>
-      <c r="B67" s="64" t="s">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A69" s="177"/>
+      <c r="B69" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C67" s="99">
-        <v>0</v>
-      </c>
-      <c r="D67" s="99">
-        <v>0</v>
-      </c>
-      <c r="E67" s="99">
-        <v>0</v>
-      </c>
-      <c r="F67" s="99">
-        <v>0</v>
-      </c>
-      <c r="G67" s="99">
-        <v>0</v>
-      </c>
-      <c r="H67" s="100">
-        <v>0</v>
-      </c>
-      <c r="I67" s="100">
-        <v>0</v>
-      </c>
-      <c r="J67" s="100">
-        <v>0</v>
-      </c>
-      <c r="K67" s="100">
-        <v>0</v>
-      </c>
-      <c r="L67" s="100">
-        <v>0</v>
-      </c>
-      <c r="M67" s="100">
-        <v>0</v>
-      </c>
-      <c r="N67" s="100">
-        <v>0</v>
-      </c>
-      <c r="O67" s="100">
-        <v>0</v>
-      </c>
-      <c r="P67" s="100">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="100">
-        <v>0</v>
-      </c>
-      <c r="R67" s="100">
-        <v>0</v>
-      </c>
-      <c r="S67" s="100">
-        <v>0</v>
-      </c>
-      <c r="T67" s="100">
-        <v>0</v>
-      </c>
-      <c r="U67" s="100">
-        <v>0</v>
-      </c>
-      <c r="V67" s="100">
-        <v>0</v>
-      </c>
-      <c r="W67" s="100">
-        <v>0</v>
-      </c>
-      <c r="X67" s="100">
-        <v>0</v>
-      </c>
-      <c r="Y67" s="100">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="100">
-        <v>0</v>
-      </c>
-      <c r="AA67" s="100">
-        <v>0</v>
-      </c>
-      <c r="AB67" s="100">
-        <v>0</v>
-      </c>
-      <c r="AC67" s="100">
-        <v>0</v>
-      </c>
-      <c r="AD67" s="100">
-        <v>0</v>
-      </c>
-      <c r="AE67" s="115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A68" s="172"/>
-      <c r="B68" s="64" t="s">
+      <c r="C69" s="99">
+        <v>0</v>
+      </c>
+      <c r="D69" s="99">
+        <v>0</v>
+      </c>
+      <c r="E69" s="99">
+        <v>0</v>
+      </c>
+      <c r="F69" s="99">
+        <v>0</v>
+      </c>
+      <c r="G69" s="99">
+        <v>0</v>
+      </c>
+      <c r="H69" s="100">
+        <v>0</v>
+      </c>
+      <c r="I69" s="100">
+        <v>0</v>
+      </c>
+      <c r="J69" s="100">
+        <v>0</v>
+      </c>
+      <c r="K69" s="100">
+        <v>0</v>
+      </c>
+      <c r="L69" s="100">
+        <v>0</v>
+      </c>
+      <c r="M69" s="100">
+        <v>0</v>
+      </c>
+      <c r="N69" s="100">
+        <v>0</v>
+      </c>
+      <c r="O69" s="100">
+        <v>0</v>
+      </c>
+      <c r="P69" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="100">
+        <v>0</v>
+      </c>
+      <c r="R69" s="100">
+        <v>0</v>
+      </c>
+      <c r="S69" s="100">
+        <v>0</v>
+      </c>
+      <c r="T69" s="100">
+        <v>0</v>
+      </c>
+      <c r="U69" s="100">
+        <v>0</v>
+      </c>
+      <c r="V69" s="100">
+        <v>0</v>
+      </c>
+      <c r="W69" s="100">
+        <v>0</v>
+      </c>
+      <c r="X69" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A70" s="177"/>
+      <c r="B70" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C68" s="99">
-        <v>0</v>
-      </c>
-      <c r="D68" s="99">
-        <v>0</v>
-      </c>
-      <c r="E68" s="99">
-        <v>0</v>
-      </c>
-      <c r="F68" s="99">
-        <v>0</v>
-      </c>
-      <c r="G68" s="99">
-        <v>0</v>
-      </c>
-      <c r="H68" s="100">
-        <v>0</v>
-      </c>
-      <c r="I68" s="100">
-        <v>0</v>
-      </c>
-      <c r="J68" s="100">
-        <v>0</v>
-      </c>
-      <c r="K68" s="100">
-        <v>0</v>
-      </c>
-      <c r="L68" s="100">
-        <v>0</v>
-      </c>
-      <c r="M68" s="100">
-        <v>0</v>
-      </c>
-      <c r="N68" s="100">
-        <v>0</v>
-      </c>
-      <c r="O68" s="100">
-        <v>0</v>
-      </c>
-      <c r="P68" s="100">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="100">
-        <v>0</v>
-      </c>
-      <c r="R68" s="100">
-        <v>0</v>
-      </c>
-      <c r="S68" s="100">
-        <v>0</v>
-      </c>
-      <c r="T68" s="100">
-        <v>0</v>
-      </c>
-      <c r="U68" s="100">
-        <v>0</v>
-      </c>
-      <c r="V68" s="100">
-        <v>0</v>
-      </c>
-      <c r="W68" s="100">
-        <v>0</v>
-      </c>
-      <c r="X68" s="100">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="100">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="100">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="100">
-        <v>0</v>
-      </c>
-      <c r="AB68" s="100">
-        <v>0</v>
-      </c>
-      <c r="AC68" s="100">
-        <v>0</v>
-      </c>
-      <c r="AD68" s="100">
-        <v>0</v>
-      </c>
-      <c r="AE68" s="115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A69" s="172"/>
-      <c r="B69" s="64" t="s">
+      <c r="C70" s="99">
+        <v>0</v>
+      </c>
+      <c r="D70" s="99">
+        <v>0</v>
+      </c>
+      <c r="E70" s="99">
+        <v>0</v>
+      </c>
+      <c r="F70" s="99">
+        <v>0</v>
+      </c>
+      <c r="G70" s="99">
+        <v>0</v>
+      </c>
+      <c r="H70" s="100">
+        <v>0</v>
+      </c>
+      <c r="I70" s="100">
+        <v>0</v>
+      </c>
+      <c r="J70" s="100">
+        <v>0</v>
+      </c>
+      <c r="K70" s="100">
+        <v>0</v>
+      </c>
+      <c r="L70" s="100">
+        <v>0</v>
+      </c>
+      <c r="M70" s="100">
+        <v>0</v>
+      </c>
+      <c r="N70" s="100">
+        <v>0</v>
+      </c>
+      <c r="O70" s="100">
+        <v>0</v>
+      </c>
+      <c r="P70" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="100">
+        <v>0</v>
+      </c>
+      <c r="R70" s="100">
+        <v>0</v>
+      </c>
+      <c r="S70" s="100">
+        <v>0</v>
+      </c>
+      <c r="T70" s="100">
+        <v>0</v>
+      </c>
+      <c r="U70" s="100">
+        <v>0</v>
+      </c>
+      <c r="V70" s="100">
+        <v>0</v>
+      </c>
+      <c r="W70" s="100">
+        <v>0</v>
+      </c>
+      <c r="X70" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="177"/>
+      <c r="B71" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C69" s="99">
-        <v>0</v>
-      </c>
-      <c r="D69" s="99">
-        <v>0</v>
-      </c>
-      <c r="E69" s="99">
-        <v>0</v>
-      </c>
-      <c r="F69" s="99">
-        <v>0</v>
-      </c>
-      <c r="G69" s="99">
-        <v>0</v>
-      </c>
-      <c r="H69" s="100">
-        <v>0</v>
-      </c>
-      <c r="I69" s="100">
-        <v>0</v>
-      </c>
-      <c r="J69" s="100">
-        <v>0</v>
-      </c>
-      <c r="K69" s="100">
-        <v>0</v>
-      </c>
-      <c r="L69" s="100">
-        <v>0</v>
-      </c>
-      <c r="M69" s="100">
-        <v>0</v>
-      </c>
-      <c r="N69" s="100">
-        <v>0</v>
-      </c>
-      <c r="O69" s="100">
-        <v>0</v>
-      </c>
-      <c r="P69" s="100">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="100">
-        <v>0</v>
-      </c>
-      <c r="R69" s="100">
-        <v>0</v>
-      </c>
-      <c r="S69" s="100">
-        <v>0</v>
-      </c>
-      <c r="T69" s="100">
-        <v>0</v>
-      </c>
-      <c r="U69" s="100">
-        <v>0</v>
-      </c>
-      <c r="V69" s="100">
-        <v>0</v>
-      </c>
-      <c r="W69" s="100">
-        <v>0</v>
-      </c>
-      <c r="X69" s="100">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="100">
-        <v>0</v>
-      </c>
-      <c r="Z69" s="100">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="100">
-        <v>0</v>
-      </c>
-      <c r="AB69" s="100">
-        <v>0</v>
-      </c>
-      <c r="AC69" s="100">
-        <v>0</v>
-      </c>
-      <c r="AD69" s="100">
-        <v>0</v>
-      </c>
-      <c r="AE69" s="115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A70" s="167" t="s">
+      <c r="C71" s="99">
+        <v>0</v>
+      </c>
+      <c r="D71" s="99">
+        <v>0</v>
+      </c>
+      <c r="E71" s="99">
+        <v>0</v>
+      </c>
+      <c r="F71" s="99">
+        <v>0</v>
+      </c>
+      <c r="G71" s="99">
+        <v>0</v>
+      </c>
+      <c r="H71" s="100">
+        <v>0</v>
+      </c>
+      <c r="I71" s="100">
+        <v>0</v>
+      </c>
+      <c r="J71" s="100">
+        <v>0</v>
+      </c>
+      <c r="K71" s="100">
+        <v>0</v>
+      </c>
+      <c r="L71" s="100">
+        <v>0</v>
+      </c>
+      <c r="M71" s="100">
+        <v>0</v>
+      </c>
+      <c r="N71" s="100">
+        <v>0</v>
+      </c>
+      <c r="O71" s="100">
+        <v>0</v>
+      </c>
+      <c r="P71" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="100">
+        <v>0</v>
+      </c>
+      <c r="R71" s="100">
+        <v>0</v>
+      </c>
+      <c r="S71" s="100">
+        <v>0</v>
+      </c>
+      <c r="T71" s="100">
+        <v>0</v>
+      </c>
+      <c r="U71" s="100">
+        <v>0</v>
+      </c>
+      <c r="V71" s="100">
+        <v>0</v>
+      </c>
+      <c r="W71" s="100">
+        <v>0</v>
+      </c>
+      <c r="X71" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A72" s="170" t="s">
+        <v>17</v>
+      </c>
+      <c r="B72" s="111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="99">
+        <v>780.16197599999998</v>
+      </c>
+      <c r="D72" s="99">
+        <v>780.16197599999998</v>
+      </c>
+      <c r="E72" s="99">
+        <v>780.16197599999998</v>
+      </c>
+      <c r="F72" s="99">
+        <v>780.16197599999998</v>
+      </c>
+      <c r="G72" s="99">
+        <v>780.16197599999998</v>
+      </c>
+      <c r="H72" s="100">
+        <v>780.16197599999998</v>
+      </c>
+      <c r="I72" s="100">
+        <v>746.04422699999998</v>
+      </c>
+      <c r="J72" s="100">
+        <v>741.11310400000002</v>
+      </c>
+      <c r="K72" s="100">
+        <v>743.12743</v>
+      </c>
+      <c r="L72" s="100">
+        <v>752.87362399999995</v>
+      </c>
+      <c r="M72" s="100">
+        <v>731.89901699999996</v>
+      </c>
+      <c r="N72" s="100">
+        <v>791.38888899999995</v>
+      </c>
+      <c r="O72" s="100">
+        <v>833.05847400000005</v>
+      </c>
+      <c r="P72" s="100">
+        <v>815.174081</v>
+      </c>
+      <c r="Q72" s="100">
+        <v>753.76851699999997</v>
+      </c>
+      <c r="R72" s="100">
+        <v>769.91370800000004</v>
+      </c>
+      <c r="S72" s="100">
+        <v>793.68268699999999</v>
+      </c>
+      <c r="T72" s="100">
+        <v>753.53923799999995</v>
+      </c>
+      <c r="U72" s="100">
+        <v>710.38523699999996</v>
+      </c>
+      <c r="V72" s="100">
+        <v>692.14456499999994</v>
+      </c>
+      <c r="W72" s="100">
+        <v>675.99433899999997</v>
+      </c>
+      <c r="X72" s="100">
+        <v>656.01309500000002</v>
+      </c>
+      <c r="Y72" s="100">
+        <v>633.72058800000002</v>
+      </c>
+      <c r="Z72" s="100">
+        <v>630.65585499999997</v>
+      </c>
+      <c r="AA72" s="100">
+        <v>617.51154499999996</v>
+      </c>
+      <c r="AB72" s="100">
+        <v>611.57758100000001</v>
+      </c>
+      <c r="AC72" s="100">
+        <v>729.93404399999997</v>
+      </c>
+      <c r="AD72" s="100">
+        <v>693.33732299999997</v>
+      </c>
+      <c r="AE72" s="115">
+        <v>628.17264699999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A73" s="170"/>
+      <c r="B73" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="99">
+        <v>0</v>
+      </c>
+      <c r="D73" s="99">
+        <v>0</v>
+      </c>
+      <c r="E73" s="99">
+        <v>0</v>
+      </c>
+      <c r="F73" s="99">
+        <v>0</v>
+      </c>
+      <c r="G73" s="99">
+        <v>0</v>
+      </c>
+      <c r="H73" s="100">
+        <v>0</v>
+      </c>
+      <c r="I73" s="100">
+        <v>0</v>
+      </c>
+      <c r="J73" s="100">
+        <v>0</v>
+      </c>
+      <c r="K73" s="100">
+        <v>0</v>
+      </c>
+      <c r="L73" s="100">
+        <v>0</v>
+      </c>
+      <c r="M73" s="100">
+        <v>0</v>
+      </c>
+      <c r="N73" s="100">
+        <v>0</v>
+      </c>
+      <c r="O73" s="100">
+        <v>0</v>
+      </c>
+      <c r="P73" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="100">
+        <v>0</v>
+      </c>
+      <c r="R73" s="100">
+        <v>0</v>
+      </c>
+      <c r="S73" s="100">
+        <v>0</v>
+      </c>
+      <c r="T73" s="100">
+        <v>0</v>
+      </c>
+      <c r="U73" s="100">
+        <v>0</v>
+      </c>
+      <c r="V73" s="100">
+        <v>0</v>
+      </c>
+      <c r="W73" s="100">
+        <v>0</v>
+      </c>
+      <c r="X73" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A74" s="170"/>
+      <c r="B74" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="99">
+        <v>2767.450652</v>
+      </c>
+      <c r="D74" s="99">
+        <v>2767.450652</v>
+      </c>
+      <c r="E74" s="99">
+        <v>2767.450652</v>
+      </c>
+      <c r="F74" s="99">
+        <v>2767.450652</v>
+      </c>
+      <c r="G74" s="99">
+        <v>2767.450652</v>
+      </c>
+      <c r="H74" s="100">
+        <v>2767.450652</v>
+      </c>
+      <c r="I74" s="100">
+        <v>2796.3821499999999</v>
+      </c>
+      <c r="J74" s="100">
+        <v>2885.9882480000001</v>
+      </c>
+      <c r="K74" s="100">
+        <v>2891.9924110000002</v>
+      </c>
+      <c r="L74" s="100">
+        <v>2971.4741290000002</v>
+      </c>
+      <c r="M74" s="100">
+        <v>2921.4435429999999</v>
+      </c>
+      <c r="N74" s="100">
+        <v>3020.1746790000002</v>
+      </c>
+      <c r="O74" s="100">
+        <v>3141.711636</v>
+      </c>
+      <c r="P74" s="100">
+        <v>2977.7809269999998</v>
+      </c>
+      <c r="Q74" s="100">
+        <v>2769.6296280000001</v>
+      </c>
+      <c r="R74" s="100">
+        <v>2723.4272019999999</v>
+      </c>
+      <c r="S74" s="100">
+        <v>2900.8420550000001</v>
+      </c>
+      <c r="T74" s="100">
+        <v>2841.8598940000002</v>
+      </c>
+      <c r="U74" s="100">
+        <v>2938.1541440000001</v>
+      </c>
+      <c r="V74" s="100">
+        <v>2932.882486</v>
+      </c>
+      <c r="W74" s="100">
+        <v>2932.633041</v>
+      </c>
+      <c r="X74" s="100">
+        <v>3094.7305630000001</v>
+      </c>
+      <c r="Y74" s="100">
+        <v>3216.8509239999998</v>
+      </c>
+      <c r="Z74" s="100">
+        <v>3317.2298559999999</v>
+      </c>
+      <c r="AA74" s="100">
+        <v>3209.0330749999998</v>
+      </c>
+      <c r="AB74" s="100">
+        <v>3284.637561</v>
+      </c>
+      <c r="AC74" s="100">
+        <v>3432.5681669999999</v>
+      </c>
+      <c r="AD74" s="100">
+        <v>3458.3788220000001</v>
+      </c>
+      <c r="AE74" s="115">
+        <v>3350.7952249999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="170"/>
+      <c r="B75" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="99">
+        <v>0</v>
+      </c>
+      <c r="D75" s="99">
+        <v>0</v>
+      </c>
+      <c r="E75" s="99">
+        <v>0</v>
+      </c>
+      <c r="F75" s="99">
+        <v>0</v>
+      </c>
+      <c r="G75" s="99">
+        <v>0</v>
+      </c>
+      <c r="H75" s="100">
+        <v>0</v>
+      </c>
+      <c r="I75" s="100">
+        <v>0</v>
+      </c>
+      <c r="J75" s="100">
+        <v>0</v>
+      </c>
+      <c r="K75" s="100">
+        <v>0</v>
+      </c>
+      <c r="L75" s="100">
+        <v>0</v>
+      </c>
+      <c r="M75" s="100">
+        <v>0</v>
+      </c>
+      <c r="N75" s="100">
+        <v>0</v>
+      </c>
+      <c r="O75" s="100">
+        <v>0</v>
+      </c>
+      <c r="P75" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="100">
+        <v>0</v>
+      </c>
+      <c r="R75" s="100">
+        <v>0</v>
+      </c>
+      <c r="S75" s="100">
+        <v>0</v>
+      </c>
+      <c r="T75" s="100">
+        <v>0</v>
+      </c>
+      <c r="U75" s="100">
+        <v>0</v>
+      </c>
+      <c r="V75" s="100">
+        <v>0</v>
+      </c>
+      <c r="W75" s="100">
+        <v>0</v>
+      </c>
+      <c r="X75" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A76" s="170" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" s="111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="99">
+        <v>51.2542355912624</v>
+      </c>
+      <c r="D76" s="99">
+        <v>51.2542355912624</v>
+      </c>
+      <c r="E76" s="99">
+        <v>51.2542355912624</v>
+      </c>
+      <c r="F76" s="99">
+        <v>51.2542355912624</v>
+      </c>
+      <c r="G76" s="99">
+        <v>51.2542355912624</v>
+      </c>
+      <c r="H76" s="100">
+        <v>51.2542355912624</v>
+      </c>
+      <c r="I76" s="100">
+        <v>55.534444556414499</v>
+      </c>
+      <c r="J76" s="100">
+        <v>51.395555046250301</v>
+      </c>
+      <c r="K76" s="100">
+        <v>46.828799270403501</v>
+      </c>
+      <c r="L76" s="100">
+        <v>46.066222222594199</v>
+      </c>
+      <c r="M76" s="100">
+        <v>44.493220926742197</v>
+      </c>
+      <c r="N76" s="100">
+        <v>45.283643136325303</v>
+      </c>
+      <c r="O76" s="100">
+        <v>44.350736499340499</v>
+      </c>
+      <c r="P76" s="100">
+        <v>44.850222620162697</v>
+      </c>
+      <c r="Q76" s="100">
+        <v>42.195649434808203</v>
+      </c>
+      <c r="R76" s="100">
+        <v>37.692640675130498</v>
+      </c>
+      <c r="S76" s="100">
+        <v>34.708631574977602</v>
+      </c>
+      <c r="T76" s="100">
+        <v>32.504488159497598</v>
+      </c>
+      <c r="U76" s="100">
+        <v>29.637390084803901</v>
+      </c>
+      <c r="V76" s="100">
+        <v>29.7244355283276</v>
+      </c>
+      <c r="W76" s="100">
+        <v>28.309007492587099</v>
+      </c>
+      <c r="X76" s="100">
+        <v>25.309779715639799</v>
+      </c>
+      <c r="Y76" s="100">
+        <v>26.4117233155397</v>
+      </c>
+      <c r="Z76" s="100">
+        <v>25.601664943580701</v>
+      </c>
+      <c r="AA76" s="100">
+        <v>24.000269160497901</v>
+      </c>
+      <c r="AB76" s="100">
+        <v>22.579428577372301</v>
+      </c>
+      <c r="AC76" s="100">
+        <v>24.649101827399999</v>
+      </c>
+      <c r="AD76" s="100">
+        <v>23.6934442895814</v>
+      </c>
+      <c r="AE76" s="115">
+        <v>22.1576325260056</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A77" s="170"/>
+      <c r="B77" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="99">
+        <v>0</v>
+      </c>
+      <c r="D77" s="99">
+        <v>0</v>
+      </c>
+      <c r="E77" s="99">
+        <v>0</v>
+      </c>
+      <c r="F77" s="99">
+        <v>0</v>
+      </c>
+      <c r="G77" s="99">
+        <v>0</v>
+      </c>
+      <c r="H77" s="100">
+        <v>0</v>
+      </c>
+      <c r="I77" s="100">
+        <v>0</v>
+      </c>
+      <c r="J77" s="100">
+        <v>0</v>
+      </c>
+      <c r="K77" s="100">
+        <v>0</v>
+      </c>
+      <c r="L77" s="100">
+        <v>0</v>
+      </c>
+      <c r="M77" s="100">
+        <v>0</v>
+      </c>
+      <c r="N77" s="100">
+        <v>0</v>
+      </c>
+      <c r="O77" s="100">
+        <v>0</v>
+      </c>
+      <c r="P77" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="100">
+        <v>0</v>
+      </c>
+      <c r="R77" s="100">
+        <v>0</v>
+      </c>
+      <c r="S77" s="100">
+        <v>0</v>
+      </c>
+      <c r="T77" s="100">
+        <v>0</v>
+      </c>
+      <c r="U77" s="100">
+        <v>0</v>
+      </c>
+      <c r="V77" s="100">
+        <v>0</v>
+      </c>
+      <c r="W77" s="100">
+        <v>0</v>
+      </c>
+      <c r="X77" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A78" s="170"/>
+      <c r="B78" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" s="99">
+        <v>0</v>
+      </c>
+      <c r="D78" s="99">
+        <v>0</v>
+      </c>
+      <c r="E78" s="99">
+        <v>0</v>
+      </c>
+      <c r="F78" s="99">
+        <v>0</v>
+      </c>
+      <c r="G78" s="99">
+        <v>0</v>
+      </c>
+      <c r="H78" s="100">
+        <v>0</v>
+      </c>
+      <c r="I78" s="100">
+        <v>0</v>
+      </c>
+      <c r="J78" s="100">
+        <v>0</v>
+      </c>
+      <c r="K78" s="100">
+        <v>0</v>
+      </c>
+      <c r="L78" s="100">
+        <v>0</v>
+      </c>
+      <c r="M78" s="100">
+        <v>0</v>
+      </c>
+      <c r="N78" s="100">
+        <v>0</v>
+      </c>
+      <c r="O78" s="100">
+        <v>0</v>
+      </c>
+      <c r="P78" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="100">
+        <v>0</v>
+      </c>
+      <c r="R78" s="100">
+        <v>0</v>
+      </c>
+      <c r="S78" s="100">
+        <v>0</v>
+      </c>
+      <c r="T78" s="100">
+        <v>0</v>
+      </c>
+      <c r="U78" s="100">
+        <v>0</v>
+      </c>
+      <c r="V78" s="100">
+        <v>0</v>
+      </c>
+      <c r="W78" s="100">
+        <v>0</v>
+      </c>
+      <c r="X78" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A79" s="170"/>
+      <c r="B79" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="99">
+        <v>0</v>
+      </c>
+      <c r="D79" s="99">
+        <v>0</v>
+      </c>
+      <c r="E79" s="99">
+        <v>0</v>
+      </c>
+      <c r="F79" s="99">
+        <v>0</v>
+      </c>
+      <c r="G79" s="99">
+        <v>0</v>
+      </c>
+      <c r="H79" s="100">
+        <v>0</v>
+      </c>
+      <c r="I79" s="100">
+        <v>0</v>
+      </c>
+      <c r="J79" s="100">
+        <v>0</v>
+      </c>
+      <c r="K79" s="100">
+        <v>0</v>
+      </c>
+      <c r="L79" s="100">
+        <v>0</v>
+      </c>
+      <c r="M79" s="100">
+        <v>0</v>
+      </c>
+      <c r="N79" s="100">
+        <v>0</v>
+      </c>
+      <c r="O79" s="100">
+        <v>0</v>
+      </c>
+      <c r="P79" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="100">
+        <v>0</v>
+      </c>
+      <c r="R79" s="100">
+        <v>0</v>
+      </c>
+      <c r="S79" s="100">
+        <v>0</v>
+      </c>
+      <c r="T79" s="100">
+        <v>0</v>
+      </c>
+      <c r="U79" s="100">
+        <v>0</v>
+      </c>
+      <c r="V79" s="100">
+        <v>0</v>
+      </c>
+      <c r="W79" s="100">
+        <v>0</v>
+      </c>
+      <c r="X79" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A80" s="170" t="s">
         <v>175</v>
       </c>
-      <c r="B70" s="64" t="s">
+      <c r="B80" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="99">
+      <c r="C80" s="99">
         <v>20483399</v>
       </c>
-      <c r="D70" s="99">
+      <c r="D80" s="99">
         <v>20483399</v>
       </c>
-      <c r="E70" s="99">
+      <c r="E80" s="99">
         <v>20483399</v>
       </c>
-      <c r="F70" s="99">
+      <c r="F80" s="99">
         <v>20483399</v>
       </c>
-      <c r="G70" s="99">
+      <c r="G80" s="99">
         <v>20483399</v>
       </c>
-      <c r="H70" s="100">
+      <c r="H80" s="100">
         <v>20483399</v>
       </c>
-      <c r="I70" s="100">
+      <c r="I80" s="100">
         <v>21142512</v>
       </c>
-      <c r="J70" s="100">
+      <c r="J80" s="100">
         <v>21439653</v>
       </c>
-      <c r="K70" s="100">
+      <c r="K80" s="100">
         <v>21839912</v>
       </c>
-      <c r="L70" s="100">
+      <c r="L80" s="100">
         <v>22319417</v>
       </c>
-      <c r="M70" s="100">
+      <c r="M80" s="100">
         <v>22831736</v>
       </c>
-      <c r="N70" s="100">
+      <c r="N80" s="100">
         <v>23356131</v>
       </c>
-      <c r="O70" s="100">
+      <c r="O80" s="100">
         <v>24476621</v>
       </c>
-      <c r="P70" s="100">
+      <c r="P80" s="100">
         <v>24676789</v>
       </c>
-      <c r="Q70" s="100">
+      <c r="Q80" s="100">
         <v>24393828</v>
       </c>
-      <c r="R70" s="100">
+      <c r="R80" s="100">
         <v>24461473</v>
       </c>
-      <c r="S70" s="100">
+      <c r="S80" s="100">
         <v>24552625</v>
       </c>
-      <c r="T70" s="100">
+      <c r="T80" s="100">
         <v>24251666</v>
       </c>
-      <c r="U70" s="100">
+      <c r="U80" s="100">
         <v>24329650</v>
       </c>
-      <c r="V70" s="100">
+      <c r="V80" s="100">
         <v>24741539</v>
       </c>
-      <c r="W70" s="100">
+      <c r="W80" s="100">
         <v>25396318</v>
       </c>
-      <c r="X70" s="100">
+      <c r="X80" s="100">
         <v>25670667</v>
       </c>
-      <c r="Y70" s="100">
+      <c r="Y80" s="100">
         <v>26002584</v>
       </c>
-      <c r="Z70" s="100">
+      <c r="Z80" s="100">
         <v>26461307</v>
       </c>
-      <c r="AA70" s="100">
+      <c r="AA80" s="100">
         <v>26997767</v>
       </c>
-      <c r="AB70" s="100">
+      <c r="AB80" s="100">
         <v>27318570</v>
       </c>
-      <c r="AC70" s="100">
+      <c r="AC80" s="100">
         <v>27742579</v>
       </c>
-      <c r="AD70" s="100">
+      <c r="AD80" s="100">
         <v>28053848</v>
       </c>
-      <c r="AE70" s="115">
+      <c r="AE80" s="115">
         <v>28460713</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A71" s="167"/>
-      <c r="B71" s="64" t="s">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A81" s="170"/>
+      <c r="B81" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C71" s="99">
+      <c r="C81" s="99">
         <v>7509</v>
       </c>
-      <c r="D71" s="99">
+      <c r="D81" s="99">
         <v>7509</v>
       </c>
-      <c r="E71" s="99">
+      <c r="E81" s="99">
         <v>7509</v>
       </c>
-      <c r="F71" s="99">
+      <c r="F81" s="99">
         <v>7509</v>
       </c>
-      <c r="G71" s="99">
+      <c r="G81" s="99">
         <v>7509</v>
       </c>
-      <c r="H71" s="100">
+      <c r="H81" s="100">
         <v>7509</v>
       </c>
-      <c r="I71" s="100">
+      <c r="I81" s="100">
         <v>8885</v>
       </c>
-      <c r="J71" s="100">
+      <c r="J81" s="100">
         <v>10724</v>
       </c>
-      <c r="K71" s="100">
+      <c r="K81" s="100">
         <v>12990</v>
       </c>
-      <c r="L71" s="100">
+      <c r="L81" s="100">
         <v>14937</v>
       </c>
-      <c r="M71" s="100">
+      <c r="M81" s="100">
         <v>17506</v>
       </c>
-      <c r="N71" s="100">
+      <c r="N81" s="100">
         <v>30914</v>
       </c>
-      <c r="O71" s="100">
+      <c r="O81" s="100">
         <v>33448</v>
       </c>
-      <c r="P71" s="100">
+      <c r="P81" s="100">
         <v>44143</v>
       </c>
-      <c r="Q71" s="100">
+      <c r="Q81" s="100">
         <v>58687</v>
       </c>
-      <c r="R71" s="100">
+      <c r="R81" s="100">
         <v>82199</v>
       </c>
-      <c r="S71" s="100">
+      <c r="S81" s="100">
         <v>82440</v>
       </c>
-      <c r="T71" s="100">
+      <c r="T81" s="100">
         <v>105390</v>
       </c>
-      <c r="U71" s="100">
+      <c r="U81" s="100">
         <v>110219</v>
       </c>
-      <c r="V71" s="100">
+      <c r="V81" s="100">
         <v>116520</v>
       </c>
-      <c r="W71" s="100">
+      <c r="W81" s="100">
         <v>127013</v>
       </c>
-      <c r="X71" s="100">
+      <c r="X81" s="100">
         <v>135211</v>
       </c>
-      <c r="Y71" s="100">
+      <c r="Y81" s="100">
         <v>140019</v>
       </c>
-      <c r="Z71" s="100">
+      <c r="Z81" s="100">
         <v>157685</v>
       </c>
-      <c r="AA71" s="100">
+      <c r="AA81" s="100">
         <v>165774</v>
       </c>
-      <c r="AB71" s="100">
+      <c r="AB81" s="100">
         <v>171926</v>
       </c>
-      <c r="AC71" s="100">
+      <c r="AC81" s="100">
         <v>172086</v>
       </c>
-      <c r="AD71" s="100">
+      <c r="AD81" s="100">
         <v>169957</v>
       </c>
-      <c r="AE71" s="115">
+      <c r="AE81" s="115">
         <v>167920</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A72" s="167"/>
-      <c r="B72" s="64" t="s">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A82" s="170"/>
+      <c r="B82" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C72" s="99">
+      <c r="C82" s="99">
         <v>5196</v>
       </c>
-      <c r="D72" s="99">
+      <c r="D82" s="99">
         <v>5196</v>
       </c>
-      <c r="E72" s="99">
+      <c r="E82" s="99">
         <v>5196</v>
       </c>
-      <c r="F72" s="99">
+      <c r="F82" s="99">
         <v>5196</v>
       </c>
-      <c r="G72" s="99">
+      <c r="G82" s="99">
         <v>5196</v>
       </c>
-      <c r="H72" s="100">
+      <c r="H82" s="100">
         <v>5196</v>
       </c>
-      <c r="I72" s="100">
+      <c r="I82" s="100">
         <v>5904</v>
       </c>
-      <c r="J72" s="100">
+      <c r="J82" s="100">
         <v>6175</v>
       </c>
-      <c r="K72" s="100">
+      <c r="K82" s="100">
         <v>6297</v>
       </c>
-      <c r="L72" s="100">
+      <c r="L82" s="100">
         <v>6483</v>
       </c>
-      <c r="M72" s="100">
+      <c r="M82" s="100">
         <v>6350</v>
       </c>
-      <c r="N72" s="100">
+      <c r="N82" s="100">
         <v>6465</v>
       </c>
-      <c r="O72" s="100">
+      <c r="O82" s="100">
         <v>6648</v>
       </c>
-      <c r="P72" s="100">
+      <c r="P82" s="100">
         <v>6259</v>
       </c>
-      <c r="Q72" s="100">
+      <c r="Q82" s="100">
         <v>6652</v>
       </c>
-      <c r="R72" s="100">
+      <c r="R82" s="100">
         <v>6390</v>
       </c>
-      <c r="S72" s="100">
+      <c r="S82" s="100">
         <v>9131</v>
       </c>
-      <c r="T72" s="100">
+      <c r="T82" s="100">
         <v>12900</v>
       </c>
-      <c r="U72" s="100">
+      <c r="U82" s="100">
         <v>16675</v>
       </c>
-      <c r="V72" s="100">
+      <c r="V82" s="100">
         <v>23954</v>
       </c>
-      <c r="W72" s="100">
+      <c r="W82" s="100">
         <v>29612</v>
       </c>
-      <c r="X72" s="100">
+      <c r="X82" s="100">
         <v>41083</v>
       </c>
-      <c r="Y72" s="100">
+      <c r="Y82" s="100">
         <v>52245</v>
       </c>
-      <c r="Z72" s="100">
+      <c r="Z82" s="100">
         <v>76495</v>
       </c>
-      <c r="AA72" s="100">
+      <c r="AA82" s="100">
         <v>98125</v>
       </c>
-      <c r="AB72" s="100">
+      <c r="AB82" s="100">
         <v>121318</v>
       </c>
-      <c r="AC72" s="100">
+      <c r="AC82" s="100">
         <v>167414</v>
       </c>
-      <c r="AD72" s="100">
+      <c r="AD82" s="100">
         <v>225112</v>
       </c>
-      <c r="AE72" s="115">
+      <c r="AE82" s="115">
         <v>308125</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A73" s="167"/>
-      <c r="B73" s="64" t="s">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A83" s="170"/>
+      <c r="B83" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C73" s="99">
-        <v>0</v>
-      </c>
-      <c r="D73" s="99">
-        <v>0</v>
-      </c>
-      <c r="E73" s="99">
-        <v>0</v>
-      </c>
-      <c r="F73" s="99">
-        <v>0</v>
-      </c>
-      <c r="G73" s="99">
-        <v>0</v>
-      </c>
-      <c r="H73" s="100">
-        <v>0</v>
-      </c>
-      <c r="I73" s="100">
-        <v>0</v>
-      </c>
-      <c r="J73" s="100">
-        <v>0</v>
-      </c>
-      <c r="K73" s="100">
-        <v>0</v>
-      </c>
-      <c r="L73" s="100">
-        <v>0</v>
-      </c>
-      <c r="M73" s="100">
-        <v>0</v>
-      </c>
-      <c r="N73" s="100">
-        <v>0</v>
-      </c>
-      <c r="O73" s="100">
-        <v>0</v>
-      </c>
-      <c r="P73" s="100">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="100">
-        <v>0</v>
-      </c>
-      <c r="R73" s="100">
-        <v>0</v>
-      </c>
-      <c r="S73" s="100">
-        <v>0</v>
-      </c>
-      <c r="T73" s="100">
-        <v>0</v>
-      </c>
-      <c r="U73" s="100">
-        <v>0</v>
-      </c>
-      <c r="V73" s="100">
-        <v>0</v>
-      </c>
-      <c r="W73" s="100">
-        <v>0</v>
-      </c>
-      <c r="X73" s="100">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="100">
-        <v>0</v>
-      </c>
-      <c r="Z73" s="100">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="100">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="100">
-        <v>0</v>
-      </c>
-      <c r="AC73" s="100">
-        <v>0</v>
-      </c>
-      <c r="AD73" s="100">
-        <v>0</v>
-      </c>
-      <c r="AE73" s="115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A74" s="173" t="s">
+      <c r="C83" s="99">
+        <v>0</v>
+      </c>
+      <c r="D83" s="99">
+        <v>0</v>
+      </c>
+      <c r="E83" s="99">
+        <v>0</v>
+      </c>
+      <c r="F83" s="99">
+        <v>0</v>
+      </c>
+      <c r="G83" s="99">
+        <v>0</v>
+      </c>
+      <c r="H83" s="100">
+        <v>0</v>
+      </c>
+      <c r="I83" s="100">
+        <v>0</v>
+      </c>
+      <c r="J83" s="100">
+        <v>0</v>
+      </c>
+      <c r="K83" s="100">
+        <v>0</v>
+      </c>
+      <c r="L83" s="100">
+        <v>0</v>
+      </c>
+      <c r="M83" s="100">
+        <v>0</v>
+      </c>
+      <c r="N83" s="100">
+        <v>0</v>
+      </c>
+      <c r="O83" s="100">
+        <v>0</v>
+      </c>
+      <c r="P83" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="100">
+        <v>0</v>
+      </c>
+      <c r="R83" s="100">
+        <v>0</v>
+      </c>
+      <c r="S83" s="100">
+        <v>0</v>
+      </c>
+      <c r="T83" s="100">
+        <v>0</v>
+      </c>
+      <c r="U83" s="100">
+        <v>0</v>
+      </c>
+      <c r="V83" s="100">
+        <v>0</v>
+      </c>
+      <c r="W83" s="100">
+        <v>0</v>
+      </c>
+      <c r="X83" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A84" s="178" t="s">
         <v>180</v>
       </c>
-      <c r="B74" s="173"/>
-      <c r="C74" s="173"/>
-      <c r="D74" s="173"/>
-      <c r="E74" s="173"/>
-      <c r="F74" s="173"/>
-      <c r="G74" s="173"/>
-      <c r="H74" s="173"/>
-      <c r="I74" s="173"/>
-      <c r="J74" s="173"/>
-      <c r="K74" s="173"/>
-      <c r="L74" s="173"/>
-      <c r="M74" s="173"/>
-      <c r="N74" s="173"/>
-      <c r="O74" s="173"/>
-      <c r="P74" s="173"/>
-      <c r="Q74" s="173"/>
-      <c r="R74" s="173"/>
-      <c r="S74" s="173"/>
-      <c r="T74" s="173"/>
-      <c r="U74" s="173"/>
-      <c r="V74" s="173"/>
-      <c r="W74" s="173"/>
-      <c r="X74" s="173"/>
-      <c r="Y74" s="173"/>
-      <c r="Z74" s="173"/>
-      <c r="AA74" s="173"/>
-      <c r="AB74" s="173"/>
-      <c r="AC74" s="173"/>
-      <c r="AD74" s="173"/>
-      <c r="AE74" s="173"/>
-    </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A75" s="167" t="s">
+      <c r="B84" s="178"/>
+      <c r="C84" s="178"/>
+      <c r="D84" s="178"/>
+      <c r="E84" s="178"/>
+      <c r="F84" s="178"/>
+      <c r="G84" s="178"/>
+      <c r="H84" s="178"/>
+      <c r="I84" s="178"/>
+      <c r="J84" s="178"/>
+      <c r="K84" s="178"/>
+      <c r="L84" s="178"/>
+      <c r="M84" s="178"/>
+      <c r="N84" s="178"/>
+      <c r="O84" s="178"/>
+      <c r="P84" s="178"/>
+      <c r="Q84" s="178"/>
+      <c r="R84" s="178"/>
+      <c r="S84" s="178"/>
+      <c r="T84" s="178"/>
+      <c r="U84" s="178"/>
+      <c r="V84" s="178"/>
+      <c r="W84" s="178"/>
+      <c r="X84" s="178"/>
+      <c r="Y84" s="178"/>
+      <c r="Z84" s="178"/>
+      <c r="AA84" s="178"/>
+      <c r="AB84" s="178"/>
+      <c r="AC84" s="178"/>
+      <c r="AD84" s="178"/>
+      <c r="AE84" s="178"/>
+    </row>
+    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A85" s="170" t="s">
         <v>181</v>
       </c>
-      <c r="B75" s="64" t="s">
+      <c r="B85" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="99">
+      <c r="C85" s="99">
         <v>614309</v>
       </c>
-      <c r="D75" s="99">
+      <c r="D85" s="99">
         <v>614309</v>
       </c>
-      <c r="E75" s="99">
+      <c r="E85" s="99">
         <v>614309</v>
       </c>
-      <c r="F75" s="99">
+      <c r="F85" s="99">
         <v>614309</v>
       </c>
-      <c r="G75" s="99">
+      <c r="G85" s="99">
         <v>614309</v>
       </c>
-      <c r="H75" s="100">
+      <c r="H85" s="100">
         <v>614309</v>
       </c>
-      <c r="I75" s="100">
+      <c r="I85" s="100">
         <v>620502</v>
       </c>
-      <c r="J75" s="100">
+      <c r="J85" s="100">
         <v>614656</v>
       </c>
-      <c r="K75" s="100">
+      <c r="K85" s="100">
         <v>616848</v>
       </c>
-      <c r="L75" s="100">
+      <c r="L85" s="100">
         <v>619355</v>
       </c>
-      <c r="M75" s="100">
+      <c r="M85" s="100">
         <v>611860</v>
       </c>
-      <c r="N75" s="100">
+      <c r="N85" s="100">
         <v>611580</v>
       </c>
-      <c r="O75" s="100">
+      <c r="O85" s="100">
         <v>611210</v>
       </c>
-      <c r="P75" s="100">
+      <c r="P85" s="100">
         <v>618423</v>
       </c>
-      <c r="Q75" s="100">
+      <c r="Q85" s="100">
         <v>617304</v>
       </c>
-      <c r="R75" s="100">
+      <c r="R85" s="100">
         <v>616213</v>
       </c>
-      <c r="S75" s="100">
+      <c r="S85" s="100">
         <v>615460</v>
       </c>
-      <c r="T75" s="100">
+      <c r="T85" s="100">
         <v>611159</v>
       </c>
-      <c r="U75" s="100">
+      <c r="U85" s="100">
         <v>599555</v>
       </c>
-      <c r="V75" s="100">
+      <c r="V85" s="100">
         <v>607099</v>
       </c>
-      <c r="W75" s="100">
+      <c r="W85" s="100">
         <v>618677</v>
       </c>
-      <c r="X75" s="100">
+      <c r="X85" s="100">
         <v>623593</v>
       </c>
-      <c r="Y75" s="100">
+      <c r="Y85" s="100">
         <v>613396</v>
       </c>
-      <c r="Z75" s="100">
+      <c r="Z85" s="100">
         <v>615406</v>
       </c>
-      <c r="AA75" s="100">
+      <c r="AA85" s="100">
         <v>631161</v>
       </c>
-      <c r="AB75" s="100">
+      <c r="AB85" s="100">
         <v>608573</v>
       </c>
-      <c r="AC75" s="100">
+      <c r="AC85" s="100">
         <v>613770</v>
       </c>
-      <c r="AD75" s="100">
+      <c r="AD85" s="100">
         <v>618632</v>
       </c>
-      <c r="AE75" s="115">
+      <c r="AE85" s="115">
         <v>619380</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A76" s="167"/>
-      <c r="B76" s="64" t="s">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A86" s="170"/>
+      <c r="B86" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="99">
+      <c r="C86" s="99">
         <v>2803</v>
       </c>
-      <c r="D76" s="99">
+      <c r="D86" s="99">
         <v>2803</v>
       </c>
-      <c r="E76" s="99">
+      <c r="E86" s="99">
         <v>2803</v>
       </c>
-      <c r="F76" s="99">
+      <c r="F86" s="99">
         <v>2803</v>
       </c>
-      <c r="G76" s="99">
+      <c r="G86" s="99">
         <v>2803</v>
       </c>
-      <c r="H76" s="100">
+      <c r="H86" s="100">
         <v>2803</v>
       </c>
-      <c r="I76" s="100">
+      <c r="I86" s="100">
         <v>4054</v>
       </c>
-      <c r="J76" s="100">
+      <c r="J86" s="100">
         <v>4530</v>
       </c>
-      <c r="K76" s="100">
+      <c r="K86" s="100">
         <v>5526</v>
       </c>
-      <c r="L76" s="100">
+      <c r="L86" s="100">
         <v>5843</v>
       </c>
-      <c r="M76" s="100">
+      <c r="M86" s="100">
         <v>7161</v>
       </c>
-      <c r="N76" s="100">
+      <c r="N86" s="100">
         <v>8045</v>
       </c>
-      <c r="O76" s="100">
+      <c r="O86" s="100">
         <v>9142</v>
       </c>
-      <c r="P76" s="100">
+      <c r="P86" s="100">
         <v>9953</v>
       </c>
-      <c r="Q76" s="100">
+      <c r="Q86" s="100">
         <v>11278</v>
       </c>
-      <c r="R76" s="100">
+      <c r="R86" s="100">
         <v>12225</v>
       </c>
-      <c r="S76" s="100">
+      <c r="S86" s="100">
         <v>15077</v>
       </c>
-      <c r="T76" s="100">
+      <c r="T86" s="100">
         <v>16284</v>
       </c>
-      <c r="U76" s="100">
+      <c r="U86" s="100">
         <v>22019</v>
       </c>
-      <c r="V76" s="100">
+      <c r="V86" s="100">
         <v>23047</v>
       </c>
-      <c r="W76" s="100">
+      <c r="W86" s="100">
         <v>25465</v>
       </c>
-      <c r="X76" s="100">
+      <c r="X86" s="100">
         <v>26604</v>
       </c>
-      <c r="Y76" s="100">
+      <c r="Y86" s="100">
         <v>28442</v>
       </c>
-      <c r="Z76" s="100">
+      <c r="Z86" s="100">
         <v>35683</v>
       </c>
-      <c r="AA76" s="100">
+      <c r="AA86" s="100">
         <v>32442</v>
       </c>
-      <c r="AB76" s="100">
+      <c r="AB86" s="100">
         <v>38203</v>
       </c>
-      <c r="AC76" s="100">
+      <c r="AC86" s="100">
         <v>43549</v>
       </c>
-      <c r="AD76" s="100">
+      <c r="AD86" s="100">
         <v>46538</v>
       </c>
-      <c r="AE76" s="115">
+      <c r="AE86" s="115">
         <v>49079</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A77" s="167"/>
-      <c r="B77" s="64" t="s">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A87" s="170"/>
+      <c r="B87" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="99">
+      <c r="C87" s="99">
         <v>1654</v>
       </c>
-      <c r="D77" s="99">
+      <c r="D87" s="99">
         <v>1654</v>
       </c>
-      <c r="E77" s="99">
+      <c r="E87" s="99">
         <v>1654</v>
       </c>
-      <c r="F77" s="99">
+      <c r="F87" s="99">
         <v>1654</v>
       </c>
-      <c r="G77" s="99">
+      <c r="G87" s="99">
         <v>1654</v>
       </c>
-      <c r="H77" s="100">
+      <c r="H87" s="100">
         <v>1654</v>
       </c>
-      <c r="I77" s="100">
+      <c r="I87" s="100">
         <v>1714</v>
       </c>
-      <c r="J77" s="100">
+      <c r="J87" s="100">
         <v>1745</v>
       </c>
-      <c r="K77" s="100">
+      <c r="K87" s="100">
         <v>1687</v>
       </c>
-      <c r="L77" s="100">
+      <c r="L87" s="100">
         <v>1690</v>
       </c>
-      <c r="M77" s="100">
+      <c r="M87" s="100">
         <v>2083</v>
       </c>
-      <c r="N77" s="100">
+      <c r="N87" s="100">
         <v>2083</v>
       </c>
-      <c r="O77" s="100">
+      <c r="O87" s="100">
         <v>2070</v>
       </c>
-      <c r="P77" s="100">
+      <c r="P87" s="100">
         <v>2082</v>
       </c>
-      <c r="Q77" s="100">
+      <c r="Q87" s="100">
         <v>2135</v>
       </c>
-      <c r="R77" s="100">
+      <c r="R87" s="100">
         <v>2469</v>
       </c>
-      <c r="S77" s="100">
+      <c r="S87" s="100">
         <v>2572</v>
       </c>
-      <c r="T77" s="100">
+      <c r="T87" s="100">
         <v>2571</v>
       </c>
-      <c r="U77" s="100">
+      <c r="U87" s="100">
         <v>4343</v>
       </c>
-      <c r="V77" s="100">
+      <c r="V87" s="100">
         <v>4623</v>
       </c>
-      <c r="W77" s="100">
+      <c r="W87" s="100">
         <v>4945</v>
       </c>
-      <c r="X77" s="100">
+      <c r="X87" s="100">
         <v>5307</v>
       </c>
-      <c r="Y77" s="100">
+      <c r="Y87" s="100">
         <v>5645</v>
       </c>
-      <c r="Z77" s="100">
+      <c r="Z87" s="100">
         <v>6079</v>
       </c>
-      <c r="AA77" s="100">
+      <c r="AA87" s="100">
         <v>7425</v>
       </c>
-      <c r="AB77" s="100">
+      <c r="AB87" s="100">
         <v>9068</v>
       </c>
-      <c r="AC77" s="100">
+      <c r="AC87" s="100">
         <v>11672</v>
       </c>
-      <c r="AD77" s="100">
+      <c r="AD87" s="100">
         <v>14809</v>
       </c>
-      <c r="AE77" s="115">
+      <c r="AE87" s="115">
         <v>20033</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A78" s="167"/>
-      <c r="B78" s="64" t="s">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A88" s="170"/>
+      <c r="B88" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C78" s="99">
-        <v>0</v>
-      </c>
-      <c r="D78" s="99">
-        <v>0</v>
-      </c>
-      <c r="E78" s="99">
-        <v>0</v>
-      </c>
-      <c r="F78" s="99">
-        <v>0</v>
-      </c>
-      <c r="G78" s="99">
-        <v>0</v>
-      </c>
-      <c r="H78" s="100">
-        <v>0</v>
-      </c>
-      <c r="I78" s="100">
-        <v>0</v>
-      </c>
-      <c r="J78" s="100">
-        <v>0</v>
-      </c>
-      <c r="K78" s="100">
-        <v>0</v>
-      </c>
-      <c r="L78" s="100">
-        <v>0</v>
-      </c>
-      <c r="M78" s="100">
-        <v>0</v>
-      </c>
-      <c r="N78" s="100">
-        <v>0</v>
-      </c>
-      <c r="O78" s="100">
-        <v>0</v>
-      </c>
-      <c r="P78" s="100">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="100">
-        <v>0</v>
-      </c>
-      <c r="R78" s="100">
-        <v>0</v>
-      </c>
-      <c r="S78" s="100">
-        <v>0</v>
-      </c>
-      <c r="T78" s="100">
-        <v>0</v>
-      </c>
-      <c r="U78" s="100">
-        <v>0</v>
-      </c>
-      <c r="V78" s="100">
-        <v>0</v>
-      </c>
-      <c r="W78" s="100">
-        <v>0</v>
-      </c>
-      <c r="X78" s="100">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="100">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="100">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="100">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="100">
-        <v>0</v>
-      </c>
-      <c r="AC78" s="100">
-        <v>0</v>
-      </c>
-      <c r="AD78" s="100">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A79" s="168" t="s">
+      <c r="C88" s="99">
+        <v>0</v>
+      </c>
+      <c r="D88" s="99">
+        <v>0</v>
+      </c>
+      <c r="E88" s="99">
+        <v>0</v>
+      </c>
+      <c r="F88" s="99">
+        <v>0</v>
+      </c>
+      <c r="G88" s="99">
+        <v>0</v>
+      </c>
+      <c r="H88" s="100">
+        <v>0</v>
+      </c>
+      <c r="I88" s="100">
+        <v>0</v>
+      </c>
+      <c r="J88" s="100">
+        <v>0</v>
+      </c>
+      <c r="K88" s="100">
+        <v>0</v>
+      </c>
+      <c r="L88" s="100">
+        <v>0</v>
+      </c>
+      <c r="M88" s="100">
+        <v>0</v>
+      </c>
+      <c r="N88" s="100">
+        <v>0</v>
+      </c>
+      <c r="O88" s="100">
+        <v>0</v>
+      </c>
+      <c r="P88" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="100">
+        <v>0</v>
+      </c>
+      <c r="R88" s="100">
+        <v>0</v>
+      </c>
+      <c r="S88" s="100">
+        <v>0</v>
+      </c>
+      <c r="T88" s="100">
+        <v>0</v>
+      </c>
+      <c r="U88" s="100">
+        <v>0</v>
+      </c>
+      <c r="V88" s="100">
+        <v>0</v>
+      </c>
+      <c r="W88" s="100">
+        <v>0</v>
+      </c>
+      <c r="X88" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A89" s="170" t="s">
+        <v>17</v>
+      </c>
+      <c r="B89" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="99">
+        <v>3992.9702010000001</v>
+      </c>
+      <c r="D89" s="99">
+        <v>3992.9702010000001</v>
+      </c>
+      <c r="E89" s="99">
+        <v>3992.9702010000001</v>
+      </c>
+      <c r="F89" s="99">
+        <v>3992.9702010000001</v>
+      </c>
+      <c r="G89" s="99">
+        <v>3992.9702010000001</v>
+      </c>
+      <c r="H89" s="100">
+        <v>3992.9702010000001</v>
+      </c>
+      <c r="I89" s="100">
+        <v>3917.1704300000001</v>
+      </c>
+      <c r="J89" s="100">
+        <v>3934.7159529999999</v>
+      </c>
+      <c r="K89" s="100">
+        <v>4121.6496619999998</v>
+      </c>
+      <c r="L89" s="100">
+        <v>4209.4294410000002</v>
+      </c>
+      <c r="M89" s="100">
+        <v>4156.5839960000003</v>
+      </c>
+      <c r="N89" s="100">
+        <v>4036.2019620000001</v>
+      </c>
+      <c r="O89" s="100">
+        <v>4090.6449010000001</v>
+      </c>
+      <c r="P89" s="100">
+        <v>4156.3702249999997</v>
+      </c>
+      <c r="Q89" s="100">
+        <v>3958.2360319999998</v>
+      </c>
+      <c r="R89" s="100">
+        <v>3869.4073979999998</v>
+      </c>
+      <c r="S89" s="100">
+        <v>3844.7569400000002</v>
+      </c>
+      <c r="T89" s="100">
+        <v>3934.102946</v>
+      </c>
+      <c r="U89" s="100">
+        <v>3838.0259350000001</v>
+      </c>
+      <c r="V89" s="100">
+        <v>3870.1517079999999</v>
+      </c>
+      <c r="W89" s="100">
+        <v>3701.2247929999999</v>
+      </c>
+      <c r="X89" s="100">
+        <v>3658.1334900000002</v>
+      </c>
+      <c r="Y89" s="100">
+        <v>3664.1381769999998</v>
+      </c>
+      <c r="Z89" s="100">
+        <v>3497.294785</v>
+      </c>
+      <c r="AA89" s="100">
+        <v>3453.0159370000001</v>
+      </c>
+      <c r="AB89" s="100">
+        <v>3136.6717910000002</v>
+      </c>
+      <c r="AC89" s="100">
+        <v>3521.9551139999999</v>
+      </c>
+      <c r="AD89" s="100">
+        <v>3380.447615</v>
+      </c>
+      <c r="AE89" s="115">
+        <v>3201.097687</v>
+      </c>
+    </row>
+    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A90" s="170"/>
+      <c r="B90" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="99">
+        <v>0</v>
+      </c>
+      <c r="D90" s="99">
+        <v>0</v>
+      </c>
+      <c r="E90" s="99">
+        <v>0</v>
+      </c>
+      <c r="F90" s="99">
+        <v>0</v>
+      </c>
+      <c r="G90" s="99">
+        <v>0</v>
+      </c>
+      <c r="H90" s="100">
+        <v>0</v>
+      </c>
+      <c r="I90" s="100">
+        <v>0</v>
+      </c>
+      <c r="J90" s="100">
+        <v>0</v>
+      </c>
+      <c r="K90" s="100">
+        <v>0</v>
+      </c>
+      <c r="L90" s="100">
+        <v>0</v>
+      </c>
+      <c r="M90" s="100">
+        <v>0</v>
+      </c>
+      <c r="N90" s="100">
+        <v>0</v>
+      </c>
+      <c r="O90" s="100">
+        <v>0</v>
+      </c>
+      <c r="P90" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="100">
+        <v>0</v>
+      </c>
+      <c r="R90" s="100">
+        <v>0</v>
+      </c>
+      <c r="S90" s="100">
+        <v>0</v>
+      </c>
+      <c r="T90" s="100">
+        <v>0</v>
+      </c>
+      <c r="U90" s="100">
+        <v>0</v>
+      </c>
+      <c r="V90" s="100">
+        <v>0</v>
+      </c>
+      <c r="W90" s="100">
+        <v>0</v>
+      </c>
+      <c r="X90" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A91" s="170"/>
+      <c r="B91" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" s="99">
+        <v>17275.046526999999</v>
+      </c>
+      <c r="D91" s="99">
+        <v>17275.046526999999</v>
+      </c>
+      <c r="E91" s="99">
+        <v>17275.046526999999</v>
+      </c>
+      <c r="F91" s="99">
+        <v>17275.046526999999</v>
+      </c>
+      <c r="G91" s="99">
+        <v>17275.046526999999</v>
+      </c>
+      <c r="H91" s="100">
+        <v>17275.046526999999</v>
+      </c>
+      <c r="I91" s="100">
+        <v>17241.645700000001</v>
+      </c>
+      <c r="J91" s="100">
+        <v>17761.315655999999</v>
+      </c>
+      <c r="K91" s="100">
+        <v>18215.366180000001</v>
+      </c>
+      <c r="L91" s="100">
+        <v>18770.725397999999</v>
+      </c>
+      <c r="M91" s="100">
+        <v>19310.849262</v>
+      </c>
+      <c r="N91" s="100">
+        <v>19391.236399000001</v>
+      </c>
+      <c r="O91" s="100">
+        <v>19781.400581999998</v>
+      </c>
+      <c r="P91" s="100">
+        <v>20365.577169</v>
+      </c>
+      <c r="Q91" s="100">
+        <v>21017.131020000001</v>
+      </c>
+      <c r="R91" s="100">
+        <v>21483.608595000002</v>
+      </c>
+      <c r="S91" s="100">
+        <v>21214.388867000001</v>
+      </c>
+      <c r="T91" s="100">
+        <v>21632.902222000001</v>
+      </c>
+      <c r="U91" s="100">
+        <v>22120.838882</v>
+      </c>
+      <c r="V91" s="100">
+        <v>22187.850998999998</v>
+      </c>
+      <c r="W91" s="100">
+        <v>22925.248178999998</v>
+      </c>
+      <c r="X91" s="100">
+        <v>23830.175514999999</v>
+      </c>
+      <c r="Y91" s="100">
+        <v>24183.327881000001</v>
+      </c>
+      <c r="Z91" s="100">
+        <v>24326.871189000001</v>
+      </c>
+      <c r="AA91" s="100">
+        <v>24055.866058</v>
+      </c>
+      <c r="AB91" s="100">
+        <v>22788.185827000001</v>
+      </c>
+      <c r="AC91" s="100">
+        <v>22836.549319999998</v>
+      </c>
+      <c r="AD91" s="100">
+        <v>23613.854671000001</v>
+      </c>
+      <c r="AE91" s="115">
+        <v>24303.341950000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A92" s="170"/>
+      <c r="B92" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" s="99">
+        <v>0</v>
+      </c>
+      <c r="D92" s="99">
+        <v>0</v>
+      </c>
+      <c r="E92" s="99">
+        <v>0</v>
+      </c>
+      <c r="F92" s="99">
+        <v>0</v>
+      </c>
+      <c r="G92" s="99">
+        <v>0</v>
+      </c>
+      <c r="H92" s="100">
+        <v>0</v>
+      </c>
+      <c r="I92" s="100">
+        <v>0</v>
+      </c>
+      <c r="J92" s="100">
+        <v>0</v>
+      </c>
+      <c r="K92" s="100">
+        <v>0</v>
+      </c>
+      <c r="L92" s="100">
+        <v>0</v>
+      </c>
+      <c r="M92" s="100">
+        <v>0</v>
+      </c>
+      <c r="N92" s="100">
+        <v>0</v>
+      </c>
+      <c r="O92" s="100">
+        <v>0</v>
+      </c>
+      <c r="P92" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="100">
+        <v>0</v>
+      </c>
+      <c r="R92" s="100">
+        <v>0</v>
+      </c>
+      <c r="S92" s="100">
+        <v>0</v>
+      </c>
+      <c r="T92" s="100">
+        <v>0</v>
+      </c>
+      <c r="U92" s="100">
+        <v>0</v>
+      </c>
+      <c r="V92" s="100">
+        <v>0</v>
+      </c>
+      <c r="W92" s="100">
+        <v>0</v>
+      </c>
+      <c r="X92" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A93" s="170" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="99">
+        <v>932.68024797032604</v>
+      </c>
+      <c r="D93" s="99">
+        <v>932.68024797032604</v>
+      </c>
+      <c r="E93" s="99">
+        <v>932.68024797032604</v>
+      </c>
+      <c r="F93" s="99">
+        <v>932.68024797032604</v>
+      </c>
+      <c r="G93" s="99">
+        <v>932.68024797032604</v>
+      </c>
+      <c r="H93" s="100">
+        <v>932.68024797032604</v>
+      </c>
+      <c r="I93" s="100">
+        <v>893.84595768382405</v>
+      </c>
+      <c r="J93" s="100">
+        <v>891.14168976822305</v>
+      </c>
+      <c r="K93" s="100">
+        <v>908.22289287278204</v>
+      </c>
+      <c r="L93" s="100">
+        <v>926.26233330613104</v>
+      </c>
+      <c r="M93" s="100">
+        <v>947.38518392273795</v>
+      </c>
+      <c r="N93" s="100">
+        <v>971.04590965456305</v>
+      </c>
+      <c r="O93" s="100">
+        <v>1000.87571825306</v>
+      </c>
+      <c r="P93" s="100">
+        <v>972.75445857435602</v>
+      </c>
+      <c r="Q93" s="100">
+        <v>928.76592290591896</v>
+      </c>
+      <c r="R93" s="100">
+        <v>885.57639527783999</v>
+      </c>
+      <c r="S93" s="100">
+        <v>908.54010180529804</v>
+      </c>
+      <c r="T93" s="100">
+        <v>856.31415061678501</v>
+      </c>
+      <c r="U93" s="100">
+        <v>796.71369895562395</v>
+      </c>
+      <c r="V93" s="100">
+        <v>743.259138417342</v>
+      </c>
+      <c r="W93" s="100">
+        <v>738.53366504973701</v>
+      </c>
+      <c r="X93" s="100">
+        <v>758.37981478619099</v>
+      </c>
+      <c r="Y93" s="100">
+        <v>771.14322332581503</v>
+      </c>
+      <c r="Z93" s="100">
+        <v>798.979942263064</v>
+      </c>
+      <c r="AA93" s="100">
+        <v>812.11051527972597</v>
+      </c>
+      <c r="AB93" s="100">
+        <v>765.69222341130899</v>
+      </c>
+      <c r="AC93" s="100">
+        <v>719.25305708554299</v>
+      </c>
+      <c r="AD93" s="100">
+        <v>732.98467754534499</v>
+      </c>
+      <c r="AE93" s="115">
+        <v>733.98644773907699</v>
+      </c>
+    </row>
+    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A94" s="170"/>
+      <c r="B94" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" s="99">
+        <v>0</v>
+      </c>
+      <c r="D94" s="99">
+        <v>0</v>
+      </c>
+      <c r="E94" s="99">
+        <v>0</v>
+      </c>
+      <c r="F94" s="99">
+        <v>0</v>
+      </c>
+      <c r="G94" s="99">
+        <v>0</v>
+      </c>
+      <c r="H94" s="100">
+        <v>0</v>
+      </c>
+      <c r="I94" s="100">
+        <v>0</v>
+      </c>
+      <c r="J94" s="100">
+        <v>0</v>
+      </c>
+      <c r="K94" s="100">
+        <v>0</v>
+      </c>
+      <c r="L94" s="100">
+        <v>0</v>
+      </c>
+      <c r="M94" s="100">
+        <v>0</v>
+      </c>
+      <c r="N94" s="100">
+        <v>0</v>
+      </c>
+      <c r="O94" s="100">
+        <v>0</v>
+      </c>
+      <c r="P94" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="100">
+        <v>0</v>
+      </c>
+      <c r="R94" s="100">
+        <v>0</v>
+      </c>
+      <c r="S94" s="100">
+        <v>0</v>
+      </c>
+      <c r="T94" s="100">
+        <v>0</v>
+      </c>
+      <c r="U94" s="100">
+        <v>0</v>
+      </c>
+      <c r="V94" s="100">
+        <v>0</v>
+      </c>
+      <c r="W94" s="100">
+        <v>0</v>
+      </c>
+      <c r="X94" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A95" s="170"/>
+      <c r="B95" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95" s="99">
+        <v>0</v>
+      </c>
+      <c r="D95" s="99">
+        <v>0</v>
+      </c>
+      <c r="E95" s="99">
+        <v>0</v>
+      </c>
+      <c r="F95" s="99">
+        <v>0</v>
+      </c>
+      <c r="G95" s="99">
+        <v>0</v>
+      </c>
+      <c r="H95" s="100">
+        <v>0</v>
+      </c>
+      <c r="I95" s="100">
+        <v>0</v>
+      </c>
+      <c r="J95" s="100">
+        <v>0</v>
+      </c>
+      <c r="K95" s="100">
+        <v>0</v>
+      </c>
+      <c r="L95" s="100">
+        <v>0</v>
+      </c>
+      <c r="M95" s="100">
+        <v>0</v>
+      </c>
+      <c r="N95" s="100">
+        <v>0</v>
+      </c>
+      <c r="O95" s="100">
+        <v>0</v>
+      </c>
+      <c r="P95" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="100">
+        <v>0</v>
+      </c>
+      <c r="R95" s="100">
+        <v>0</v>
+      </c>
+      <c r="S95" s="100">
+        <v>0</v>
+      </c>
+      <c r="T95" s="100">
+        <v>0</v>
+      </c>
+      <c r="U95" s="100">
+        <v>0</v>
+      </c>
+      <c r="V95" s="100">
+        <v>0</v>
+      </c>
+      <c r="W95" s="100">
+        <v>0</v>
+      </c>
+      <c r="X95" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A96" s="170"/>
+      <c r="B96" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C96" s="99">
+        <v>0</v>
+      </c>
+      <c r="D96" s="99">
+        <v>0</v>
+      </c>
+      <c r="E96" s="99">
+        <v>0</v>
+      </c>
+      <c r="F96" s="99">
+        <v>0</v>
+      </c>
+      <c r="G96" s="99">
+        <v>0</v>
+      </c>
+      <c r="H96" s="100">
+        <v>0</v>
+      </c>
+      <c r="I96" s="100">
+        <v>0</v>
+      </c>
+      <c r="J96" s="100">
+        <v>0</v>
+      </c>
+      <c r="K96" s="100">
+        <v>0</v>
+      </c>
+      <c r="L96" s="100">
+        <v>0</v>
+      </c>
+      <c r="M96" s="100">
+        <v>0</v>
+      </c>
+      <c r="N96" s="100">
+        <v>0</v>
+      </c>
+      <c r="O96" s="100">
+        <v>0</v>
+      </c>
+      <c r="P96" s="100">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="100">
+        <v>0</v>
+      </c>
+      <c r="R96" s="100">
+        <v>0</v>
+      </c>
+      <c r="S96" s="100">
+        <v>0</v>
+      </c>
+      <c r="T96" s="100">
+        <v>0</v>
+      </c>
+      <c r="U96" s="100">
+        <v>0</v>
+      </c>
+      <c r="V96" s="100">
+        <v>0</v>
+      </c>
+      <c r="W96" s="100">
+        <v>0</v>
+      </c>
+      <c r="X96" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="100">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="100">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="100">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="100">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="100">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="171" t="s">
         <v>182</v>
       </c>
-      <c r="B79" s="64" t="s">
+      <c r="B97" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="C79" s="99">
+      <c r="C97" s="99">
         <v>175807826</v>
       </c>
-      <c r="D79" s="99">
+      <c r="D97" s="99">
         <v>175807826</v>
       </c>
-      <c r="E79" s="99">
+      <c r="E97" s="99">
         <v>175807826</v>
       </c>
-      <c r="F79" s="99">
+      <c r="F97" s="99">
         <v>175807826</v>
       </c>
-      <c r="G79" s="99">
+      <c r="G97" s="99">
         <v>175807826</v>
       </c>
-      <c r="H79" s="100">
+      <c r="H97" s="100">
         <v>175807826</v>
       </c>
-      <c r="I79" s="100">
+      <c r="I97" s="100">
         <v>179960723</v>
       </c>
-      <c r="J79" s="100">
+      <c r="J97" s="100">
         <v>183153191</v>
       </c>
-      <c r="K79" s="100">
+      <c r="K97" s="100">
         <v>186130036</v>
       </c>
-      <c r="L79" s="100">
+      <c r="L97" s="100">
         <v>188593766</v>
       </c>
-      <c r="M79" s="100">
+      <c r="M97" s="100">
         <v>192403683</v>
       </c>
-      <c r="N79" s="100">
+      <c r="N97" s="100">
         <v>197055973</v>
       </c>
-      <c r="O79" s="100">
+      <c r="O97" s="100">
         <v>201530856</v>
       </c>
-      <c r="P79" s="100">
+      <c r="P97" s="100">
         <v>206317391</v>
       </c>
-      <c r="Q79" s="100">
+      <c r="Q97" s="100">
         <v>208772790</v>
       </c>
-      <c r="R79" s="100">
+      <c r="R97" s="100">
         <v>212873554</v>
       </c>
-      <c r="S79" s="100">
+      <c r="S97" s="100">
         <v>217091964</v>
       </c>
-      <c r="T79" s="100">
+      <c r="T97" s="100">
         <v>219023668</v>
       </c>
-      <c r="U79" s="100">
+      <c r="U97" s="100">
         <v>221230717</v>
       </c>
-      <c r="V79" s="100">
+      <c r="V97" s="100">
         <v>224342237</v>
       </c>
-      <c r="W79" s="100">
+      <c r="W97" s="100">
         <v>228236064</v>
       </c>
-      <c r="X79" s="100">
+      <c r="X97" s="100">
         <v>232760565</v>
       </c>
-      <c r="Y79" s="100">
+      <c r="Y97" s="100">
         <v>238553938</v>
       </c>
-      <c r="Z79" s="100">
+      <c r="Z97" s="100">
         <v>242507151</v>
       </c>
-      <c r="AA79" s="100">
+      <c r="AA97" s="100">
         <v>246922936</v>
       </c>
-      <c r="AB79" s="100">
+      <c r="AB97" s="100">
         <v>248847531</v>
       </c>
-      <c r="AC79" s="100">
+      <c r="AC97" s="100">
         <v>250134379</v>
       </c>
-      <c r="AD79" s="100">
+      <c r="AD97" s="100">
         <v>250513956</v>
       </c>
-      <c r="AE79" s="115">
+      <c r="AE97" s="115">
         <v>252053030</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A80" s="168"/>
-      <c r="B80" s="64" t="s">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A98" s="171"/>
+      <c r="B98" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C80" s="99">
+      <c r="C98" s="99">
         <v>289200</v>
       </c>
-      <c r="D80" s="99">
+      <c r="D98" s="99">
         <v>289200</v>
       </c>
-      <c r="E80" s="99">
+      <c r="E98" s="99">
         <v>289200</v>
       </c>
-      <c r="F80" s="99">
+      <c r="F98" s="99">
         <v>289200</v>
       </c>
-      <c r="G80" s="99">
+      <c r="G98" s="99">
         <v>289200</v>
       </c>
-      <c r="H80" s="100">
+      <c r="H98" s="100">
         <v>289200</v>
       </c>
-      <c r="I80" s="100">
+      <c r="I98" s="100">
         <v>338214</v>
       </c>
-      <c r="J80" s="100">
+      <c r="J98" s="100">
         <v>339532</v>
       </c>
-      <c r="K80" s="100">
+      <c r="K98" s="100">
         <v>349364</v>
       </c>
-      <c r="L80" s="100">
+      <c r="L98" s="100">
         <v>335602</v>
       </c>
-      <c r="M80" s="100">
+      <c r="M98" s="100">
         <v>420862</v>
       </c>
-      <c r="N80" s="100">
+      <c r="N98" s="100">
         <v>483242</v>
       </c>
-      <c r="O80" s="100">
+      <c r="O98" s="100">
         <v>553242</v>
       </c>
-      <c r="P80" s="100">
+      <c r="P98" s="100">
         <v>605633</v>
       </c>
-      <c r="Q80" s="100">
+      <c r="Q98" s="100">
         <v>764039</v>
       </c>
-      <c r="R80" s="100">
+      <c r="R98" s="100">
         <v>849985</v>
       </c>
-      <c r="S80" s="100">
+      <c r="S98" s="100">
         <v>874684</v>
       </c>
-      <c r="T80" s="100">
+      <c r="T98" s="100">
         <v>934994</v>
       </c>
-      <c r="U80" s="100">
+      <c r="U98" s="100">
         <v>1004586</v>
       </c>
-      <c r="V80" s="100">
+      <c r="V98" s="100">
         <v>1106815</v>
       </c>
-      <c r="W80" s="100">
+      <c r="W98" s="100">
         <v>1161042</v>
       </c>
-      <c r="X80" s="100">
+      <c r="X98" s="100">
         <v>1186655</v>
       </c>
-      <c r="Y80" s="100">
+      <c r="Y98" s="100">
         <v>1209398</v>
       </c>
-      <c r="Z80" s="100">
+      <c r="Z98" s="100">
         <v>1257688</v>
       </c>
-      <c r="AA80" s="100">
+      <c r="AA98" s="100">
         <v>1299808</v>
       </c>
-      <c r="AB80" s="100">
+      <c r="AB98" s="100">
         <v>1332591</v>
       </c>
-      <c r="AC80" s="100">
+      <c r="AC98" s="100">
         <v>1326853</v>
       </c>
-      <c r="AD80" s="100">
+      <c r="AD98" s="100">
         <v>1314245</v>
       </c>
-      <c r="AE80" s="115">
+      <c r="AE98" s="115">
         <v>1324235</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A81" s="168"/>
-      <c r="B81" s="64" t="s">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A99" s="171"/>
+      <c r="B99" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C81" s="99">
-        <v>0</v>
-      </c>
-      <c r="D81" s="99">
-        <v>0</v>
-      </c>
-      <c r="E81" s="99">
-        <v>0</v>
-      </c>
-      <c r="F81" s="99">
-        <v>0</v>
-      </c>
-      <c r="G81" s="99">
-        <v>0</v>
-      </c>
-      <c r="H81" s="100">
-        <v>0</v>
-      </c>
-      <c r="I81" s="100">
-        <v>0</v>
-      </c>
-      <c r="J81" s="100">
-        <v>0</v>
-      </c>
-      <c r="K81" s="100">
+      <c r="C99" s="99">
+        <v>0</v>
+      </c>
+      <c r="D99" s="99">
+        <v>0</v>
+      </c>
+      <c r="E99" s="99">
+        <v>0</v>
+      </c>
+      <c r="F99" s="99">
+        <v>0</v>
+      </c>
+      <c r="G99" s="99">
+        <v>0</v>
+      </c>
+      <c r="H99" s="100">
+        <v>0</v>
+      </c>
+      <c r="I99" s="100">
+        <v>0</v>
+      </c>
+      <c r="J99" s="100">
+        <v>0</v>
+      </c>
+      <c r="K99" s="100">
         <v>9</v>
       </c>
-      <c r="L81" s="100">
+      <c r="L99" s="100">
         <v>13</v>
       </c>
-      <c r="M81" s="100">
+      <c r="M99" s="100">
         <v>15</v>
       </c>
-      <c r="N81" s="100">
+      <c r="N99" s="100">
         <v>50</v>
       </c>
-      <c r="O81" s="100">
+      <c r="O99" s="100">
         <v>76</v>
       </c>
-      <c r="P81" s="100">
+      <c r="P99" s="100">
         <v>4109</v>
       </c>
-      <c r="Q81" s="100">
+      <c r="Q99" s="100">
         <v>4826</v>
       </c>
-      <c r="R81" s="100">
+      <c r="R99" s="100">
         <v>10790</v>
       </c>
-      <c r="S81" s="100">
+      <c r="S99" s="100">
         <v>24790</v>
       </c>
-      <c r="T81" s="100">
+      <c r="T99" s="100">
         <v>33975</v>
       </c>
-      <c r="U81" s="100">
+      <c r="U99" s="100">
         <v>54080</v>
       </c>
-      <c r="V81" s="100">
+      <c r="V99" s="100">
         <v>80852</v>
       </c>
-      <c r="W81" s="100">
+      <c r="W99" s="100">
         <v>121438</v>
       </c>
-      <c r="X81" s="100">
+      <c r="X99" s="100">
         <v>172975</v>
       </c>
-      <c r="Y81" s="100">
+      <c r="Y99" s="100">
         <v>259104</v>
       </c>
-      <c r="Z81" s="100">
+      <c r="Z99" s="100">
         <v>394115</v>
       </c>
-      <c r="AA81" s="100">
+      <c r="AA99" s="100">
         <v>640507</v>
       </c>
-      <c r="AB81" s="100">
+      <c r="AB99" s="100">
         <v>1153299</v>
       </c>
-      <c r="AC81" s="100">
+      <c r="AC99" s="100">
         <v>2049970</v>
       </c>
-      <c r="AD81" s="100">
+      <c r="AD99" s="100">
         <v>3039112</v>
       </c>
-      <c r="AE81" s="115">
+      <c r="AE99" s="115">
         <v>4306401</v>
       </c>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A82" s="168"/>
-      <c r="B82" s="108" t="s">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A100" s="171"/>
+      <c r="B100" s="108" t="s">
         <v>83</v>
       </c>
-      <c r="C82" s="116">
-        <v>0</v>
-      </c>
-      <c r="D82" s="116">
-        <v>0</v>
-      </c>
-      <c r="E82" s="116">
-        <v>0</v>
-      </c>
-      <c r="F82" s="116">
-        <v>0</v>
-      </c>
-      <c r="G82" s="116">
-        <v>0</v>
-      </c>
-      <c r="H82" s="117">
-        <v>0</v>
-      </c>
-      <c r="I82" s="117">
-        <v>0</v>
-      </c>
-      <c r="J82" s="117">
-        <v>0</v>
-      </c>
-      <c r="K82" s="117">
-        <v>0</v>
-      </c>
-      <c r="L82" s="117">
-        <v>0</v>
-      </c>
-      <c r="M82" s="117">
-        <v>0</v>
-      </c>
-      <c r="N82" s="117">
-        <v>0</v>
-      </c>
-      <c r="O82" s="117">
-        <v>0</v>
-      </c>
-      <c r="P82" s="117">
+      <c r="C100" s="116">
+        <v>0</v>
+      </c>
+      <c r="D100" s="116">
+        <v>0</v>
+      </c>
+      <c r="E100" s="116">
+        <v>0</v>
+      </c>
+      <c r="F100" s="116">
+        <v>0</v>
+      </c>
+      <c r="G100" s="116">
+        <v>0</v>
+      </c>
+      <c r="H100" s="117">
+        <v>0</v>
+      </c>
+      <c r="I100" s="117">
+        <v>0</v>
+      </c>
+      <c r="J100" s="117">
+        <v>0</v>
+      </c>
+      <c r="K100" s="117">
+        <v>0</v>
+      </c>
+      <c r="L100" s="117">
+        <v>0</v>
+      </c>
+      <c r="M100" s="117">
+        <v>0</v>
+      </c>
+      <c r="N100" s="117">
+        <v>0</v>
+      </c>
+      <c r="O100" s="117">
+        <v>0</v>
+      </c>
+      <c r="P100" s="117">
         <v>130</v>
       </c>
-      <c r="Q82" s="117">
+      <c r="Q100" s="117">
         <v>160</v>
       </c>
-      <c r="R82" s="117">
+      <c r="R100" s="117">
         <v>378</v>
       </c>
-      <c r="S82" s="117">
+      <c r="S100" s="117">
         <v>918</v>
       </c>
-      <c r="T82" s="117">
+      <c r="T100" s="117">
         <v>9376</v>
       </c>
-      <c r="U82" s="117">
+      <c r="U100" s="117">
         <v>48400</v>
       </c>
-      <c r="V82" s="117">
+      <c r="V100" s="117">
         <v>94991</v>
       </c>
-      <c r="W82" s="117">
+      <c r="W100" s="117">
         <v>170532</v>
       </c>
-      <c r="X82" s="117">
+      <c r="X100" s="117">
         <v>228307</v>
       </c>
-      <c r="Y82" s="117">
+      <c r="Y100" s="117">
         <v>296493</v>
       </c>
-      <c r="Z82" s="117">
+      <c r="Z100" s="117">
         <v>395630</v>
       </c>
-      <c r="AA82" s="117">
+      <c r="AA100" s="117">
         <v>533349</v>
       </c>
-      <c r="AB82" s="117">
+      <c r="AB100" s="117">
         <v>1027123</v>
       </c>
-      <c r="AC82" s="117">
+      <c r="AC100" s="117">
         <v>1925274</v>
       </c>
-      <c r="AD82" s="117">
+      <c r="AD100" s="117">
         <v>2819072</v>
       </c>
-      <c r="AE82" s="118">
+      <c r="AE100" s="118">
         <v>3515624</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A83" s="109"/>
-      <c r="C83" s="110"/>
-    </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A84" s="109"/>
-      <c r="C84" s="110"/>
-    </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A85" s="109"/>
-      <c r="C85" s="110"/>
-    </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A89" s="119"/>
-      <c r="B89" s="120"/>
-      <c r="C89" s="120">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A101" s="109"/>
+      <c r="C101" s="110"/>
+    </row>
+    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A102" s="109"/>
+      <c r="C102" s="110"/>
+    </row>
+    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A103" s="109"/>
+      <c r="C103" s="110"/>
+    </row>
+    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A107" s="119"/>
+      <c r="B107" s="120"/>
+      <c r="C107" s="120">
         <v>1995</v>
       </c>
-      <c r="D89" s="120">
+      <c r="D107" s="120">
         <v>2015</v>
       </c>
-      <c r="E89" s="120">
+      <c r="E107" s="120">
         <v>2016</v>
       </c>
-      <c r="F89" s="120">
+      <c r="F107" s="120">
         <v>2017</v>
       </c>
-      <c r="G89" s="120">
+      <c r="G107" s="120">
         <v>2018</v>
       </c>
-      <c r="H89" s="120">
+      <c r="H107" s="120">
         <v>2019</v>
       </c>
-      <c r="I89" s="120">
+      <c r="I107" s="120">
         <v>2020</v>
       </c>
-      <c r="J89" s="120">
+      <c r="J107" s="120">
         <v>2021</v>
       </c>
-      <c r="K89" s="120">
+      <c r="K107" s="120">
         <v>2022</v>
       </c>
-      <c r="L89" s="121">
+      <c r="L107" s="121">
         <v>2023</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A90" s="174" t="s">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A108" s="174" t="s">
         <v>183</v>
       </c>
-      <c r="B90" s="122" t="s">
+      <c r="B108" s="122" t="s">
         <v>184</v>
       </c>
-      <c r="C90" s="123">
+      <c r="C108" s="123">
         <v>0.85</v>
       </c>
-      <c r="D90" s="123">
+      <c r="D108" s="123">
         <v>0.85</v>
       </c>
-      <c r="E90" s="123">
+      <c r="E108" s="123">
         <v>0.84</v>
       </c>
-      <c r="F90" s="123">
+      <c r="F108" s="123">
         <v>0.8</v>
       </c>
-      <c r="G90" s="123">
+      <c r="G108" s="123">
         <v>0.6</v>
       </c>
-      <c r="H90" s="124">
+      <c r="H108" s="124">
         <v>0.4</v>
       </c>
-      <c r="I90" s="124">
+      <c r="I108" s="124">
         <v>0.15</v>
       </c>
-      <c r="J90" s="124">
+      <c r="J108" s="124">
         <v>0.05</v>
       </c>
-      <c r="K90" s="124">
+      <c r="K108" s="124">
         <v>0.02</v>
       </c>
-      <c r="L90" s="125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A91" s="174"/>
-      <c r="B91" s="122" t="s">
+      <c r="L108" s="125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A109" s="174"/>
+      <c r="B109" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="C91" s="126">
+      <c r="C109" s="126">
         <v>0.01</v>
       </c>
-      <c r="D91" s="126">
+      <c r="D109" s="126">
         <v>0.01</v>
       </c>
-      <c r="E91" s="124">
+      <c r="E109" s="124">
         <v>0.01</v>
       </c>
-      <c r="F91" s="124">
+      <c r="F109" s="124">
         <v>0.01</v>
       </c>
-      <c r="G91" s="124">
+      <c r="G109" s="124">
         <v>0.02</v>
       </c>
-      <c r="H91" s="124">
+      <c r="H109" s="124">
         <v>0.03</v>
       </c>
-      <c r="I91" s="124">
+      <c r="I109" s="124">
         <v>0.05</v>
       </c>
-      <c r="J91" s="124">
+      <c r="J109" s="124">
         <v>0.15</v>
       </c>
-      <c r="K91" s="124">
+      <c r="K109" s="124">
         <v>0.28000000000000003</v>
       </c>
-      <c r="L91" s="127">
+      <c r="L109" s="127">
         <v>0.32</v>
       </c>
     </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A92" s="174"/>
-      <c r="B92" s="122" t="s">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A110" s="174"/>
+      <c r="B110" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="C92" s="124">
-        <v>0</v>
-      </c>
-      <c r="D92" s="124">
-        <v>0</v>
-      </c>
-      <c r="E92" s="124">
-        <v>0</v>
-      </c>
-      <c r="F92" s="124">
+      <c r="C110" s="124">
+        <v>0</v>
+      </c>
+      <c r="D110" s="124">
+        <v>0</v>
+      </c>
+      <c r="E110" s="124">
+        <v>0</v>
+      </c>
+      <c r="F110" s="124">
         <v>0.05</v>
       </c>
-      <c r="G92" s="124">
+      <c r="G110" s="124">
         <v>0.2</v>
       </c>
-      <c r="H92" s="123">
+      <c r="H110" s="123">
         <v>0.4</v>
       </c>
-      <c r="I92" s="123">
+      <c r="I110" s="123">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J92" s="124">
+      <c r="J110" s="124">
         <v>0.4</v>
       </c>
-      <c r="K92" s="124">
+      <c r="K110" s="124">
         <v>0.2</v>
       </c>
-      <c r="L92" s="125">
+      <c r="L110" s="125">
         <v>0.15</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A93" s="174"/>
-      <c r="B93" s="122" t="s">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A111" s="174"/>
+      <c r="B111" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="C93" s="124">
-        <v>0</v>
-      </c>
-      <c r="D93" s="124">
-        <v>0</v>
-      </c>
-      <c r="E93" s="124">
-        <v>0</v>
-      </c>
-      <c r="F93" s="124">
-        <v>0</v>
-      </c>
-      <c r="G93" s="124">
-        <v>0</v>
-      </c>
-      <c r="H93" s="124">
+      <c r="C111" s="124">
+        <v>0</v>
+      </c>
+      <c r="D111" s="124">
+        <v>0</v>
+      </c>
+      <c r="E111" s="124">
+        <v>0</v>
+      </c>
+      <c r="F111" s="124">
+        <v>0</v>
+      </c>
+      <c r="G111" s="124">
+        <v>0</v>
+      </c>
+      <c r="H111" s="124">
         <v>0.02</v>
       </c>
-      <c r="I93" s="124">
+      <c r="I111" s="124">
         <v>0.1</v>
       </c>
-      <c r="J93" s="124">
+      <c r="J111" s="124">
         <v>0.25</v>
       </c>
-      <c r="K93" s="123">
+      <c r="K111" s="123">
         <v>0.38</v>
       </c>
-      <c r="L93" s="127">
+      <c r="L111" s="127">
         <v>0.43</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A94" s="174"/>
-      <c r="B94" s="128" t="s">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A112" s="174"/>
+      <c r="B112" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="C94" s="129">
+      <c r="C112" s="129">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D94" s="129">
+      <c r="D112" s="129">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E94" s="129">
+      <c r="E112" s="129">
         <v>0.15</v>
       </c>
-      <c r="F94" s="129">
+      <c r="F112" s="129">
         <v>0.14000000000000001</v>
       </c>
-      <c r="G94" s="129">
+      <c r="G112" s="129">
         <v>0.18</v>
       </c>
-      <c r="H94" s="129">
+      <c r="H112" s="129">
         <v>0.15</v>
       </c>
-      <c r="I94" s="129">
+      <c r="I112" s="129">
         <v>0.15</v>
       </c>
-      <c r="J94" s="129">
+      <c r="J112" s="129">
         <v>0.15</v>
       </c>
-      <c r="K94" s="129">
+      <c r="K112" s="129">
         <v>0.12</v>
       </c>
-      <c r="L94" s="130">
+      <c r="L112" s="130">
         <v>0.1</v>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A95" s="174" t="s">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" s="174" t="s">
         <v>185</v>
       </c>
-      <c r="B95" s="122" t="s">
+      <c r="B113" s="122" t="s">
         <v>184</v>
       </c>
-      <c r="C95" s="131">
+      <c r="C113" s="131">
         <v>0.95</v>
       </c>
-      <c r="D95" s="131">
+      <c r="D113" s="131">
         <v>0.85</v>
       </c>
-      <c r="E95" s="131">
+      <c r="E113" s="131">
         <v>0.8</v>
       </c>
-      <c r="F95" s="131">
+      <c r="F113" s="131">
         <v>0.6</v>
       </c>
-      <c r="G95" s="131">
+      <c r="G113" s="131">
         <v>0.4</v>
       </c>
-      <c r="H95" s="131">
+      <c r="H113" s="131">
         <v>0.2</v>
       </c>
-      <c r="I95" s="131">
+      <c r="I113" s="131">
         <v>0.05</v>
       </c>
-      <c r="J95" s="131">
-        <v>0</v>
-      </c>
-      <c r="K95" s="131">
-        <v>0</v>
-      </c>
-      <c r="L95" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A96" s="174"/>
-      <c r="B96" s="122" t="s">
+      <c r="J113" s="131">
+        <v>0</v>
+      </c>
+      <c r="K113" s="131">
+        <v>0</v>
+      </c>
+      <c r="L113" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" s="174"/>
+      <c r="B114" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="C96" s="131">
+      <c r="C114" s="131">
         <v>0.05</v>
       </c>
-      <c r="D96" s="131">
+      <c r="D114" s="131">
         <v>0.15</v>
       </c>
-      <c r="E96" s="131">
+      <c r="E114" s="131">
         <v>0.2</v>
       </c>
-      <c r="F96" s="131">
+      <c r="F114" s="131">
         <v>0.25</v>
       </c>
-      <c r="G96" s="131">
+      <c r="G114" s="131">
         <v>0.3</v>
       </c>
-      <c r="H96" s="131">
+      <c r="H114" s="131">
         <v>0.35</v>
       </c>
-      <c r="I96" s="131">
+      <c r="I114" s="131">
         <v>0.4</v>
       </c>
-      <c r="J96" s="131">
+      <c r="J114" s="131">
         <v>0.45</v>
       </c>
-      <c r="K96" s="131">
+      <c r="K114" s="131">
         <v>0.5</v>
       </c>
-      <c r="L96" s="132">
+      <c r="L114" s="132">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="174"/>
-      <c r="B97" s="122" t="s">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" s="174"/>
+      <c r="B115" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="C97" s="131">
-        <v>0</v>
-      </c>
-      <c r="D97" s="131">
-        <v>0</v>
-      </c>
-      <c r="E97" s="131">
-        <v>0</v>
-      </c>
-      <c r="F97" s="131">
+      <c r="C115" s="131">
+        <v>0</v>
+      </c>
+      <c r="D115" s="131">
+        <v>0</v>
+      </c>
+      <c r="E115" s="131">
+        <v>0</v>
+      </c>
+      <c r="F115" s="131">
         <v>0.15</v>
       </c>
-      <c r="G97" s="131">
+      <c r="G115" s="131">
         <v>0.3</v>
       </c>
-      <c r="H97" s="131">
+      <c r="H115" s="131">
         <v>0.45</v>
       </c>
-      <c r="I97" s="131">
+      <c r="I115" s="131">
         <v>0.5</v>
       </c>
-      <c r="J97" s="131">
+      <c r="J115" s="131">
         <v>0.45</v>
       </c>
-      <c r="K97" s="131">
+      <c r="K115" s="131">
         <v>0.35</v>
       </c>
-      <c r="L97" s="132">
+      <c r="L115" s="132">
         <v>0.25</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="174"/>
-      <c r="B98" s="122" t="s">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" s="174"/>
+      <c r="B116" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="C98" s="131">
-        <v>0</v>
-      </c>
-      <c r="D98" s="131">
-        <v>0</v>
-      </c>
-      <c r="E98" s="131">
-        <v>0</v>
-      </c>
-      <c r="F98" s="131">
-        <v>0</v>
-      </c>
-      <c r="G98" s="131">
-        <v>0</v>
-      </c>
-      <c r="H98" s="131">
-        <v>0</v>
-      </c>
-      <c r="I98" s="131">
+      <c r="C116" s="131">
+        <v>0</v>
+      </c>
+      <c r="D116" s="131">
+        <v>0</v>
+      </c>
+      <c r="E116" s="131">
+        <v>0</v>
+      </c>
+      <c r="F116" s="131">
+        <v>0</v>
+      </c>
+      <c r="G116" s="131">
+        <v>0</v>
+      </c>
+      <c r="H116" s="131">
+        <v>0</v>
+      </c>
+      <c r="I116" s="131">
         <v>0.05</v>
       </c>
-      <c r="J98" s="131">
+      <c r="J116" s="131">
         <v>0.1</v>
       </c>
-      <c r="K98" s="131">
+      <c r="K116" s="131">
         <v>0.15</v>
       </c>
-      <c r="L98" s="132">
+      <c r="L116" s="132">
         <v>0.2</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="174"/>
-      <c r="B99" s="128" t="s">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" s="174"/>
+      <c r="B117" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="C99" s="131">
-        <v>0</v>
-      </c>
-      <c r="D99" s="131">
-        <v>0</v>
-      </c>
-      <c r="E99" s="131">
-        <v>0</v>
-      </c>
-      <c r="F99" s="131">
-        <v>0</v>
-      </c>
-      <c r="G99" s="131">
-        <v>0</v>
-      </c>
-      <c r="H99" s="131">
-        <v>0</v>
-      </c>
-      <c r="I99" s="131">
-        <v>0</v>
-      </c>
-      <c r="J99" s="131">
-        <v>0</v>
-      </c>
-      <c r="K99" s="131">
-        <v>0</v>
-      </c>
-      <c r="L99" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="174" t="s">
+      <c r="C117" s="131">
+        <v>0</v>
+      </c>
+      <c r="D117" s="131">
+        <v>0</v>
+      </c>
+      <c r="E117" s="131">
+        <v>0</v>
+      </c>
+      <c r="F117" s="131">
+        <v>0</v>
+      </c>
+      <c r="G117" s="131">
+        <v>0</v>
+      </c>
+      <c r="H117" s="131">
+        <v>0</v>
+      </c>
+      <c r="I117" s="131">
+        <v>0</v>
+      </c>
+      <c r="J117" s="131">
+        <v>0</v>
+      </c>
+      <c r="K117" s="131">
+        <v>0</v>
+      </c>
+      <c r="L117" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" s="174" t="s">
         <v>186</v>
       </c>
-      <c r="B100" s="122" t="s">
+      <c r="B118" s="122" t="s">
         <v>184</v>
       </c>
-      <c r="C100" s="131">
+      <c r="C118" s="131">
         <v>0.95</v>
       </c>
-      <c r="D100" s="131">
+      <c r="D118" s="131">
         <v>0.85</v>
       </c>
-      <c r="E100" s="131">
+      <c r="E118" s="131">
         <v>0.8</v>
       </c>
-      <c r="F100" s="131">
+      <c r="F118" s="131">
         <v>0.6</v>
       </c>
-      <c r="G100" s="131">
+      <c r="G118" s="131">
         <v>0.4</v>
       </c>
-      <c r="H100" s="131">
+      <c r="H118" s="131">
         <v>0.2</v>
       </c>
-      <c r="I100" s="131">
+      <c r="I118" s="131">
         <v>0.05</v>
       </c>
-      <c r="J100" s="131">
-        <v>0</v>
-      </c>
-      <c r="K100" s="131">
-        <v>0</v>
-      </c>
-      <c r="L100" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="174"/>
-      <c r="B101" s="122" t="s">
+      <c r="J118" s="131">
+        <v>0</v>
+      </c>
+      <c r="K118" s="131">
+        <v>0</v>
+      </c>
+      <c r="L118" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" s="174"/>
+      <c r="B119" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="C101" s="131">
+      <c r="C119" s="131">
         <v>0.05</v>
       </c>
-      <c r="D101" s="131">
+      <c r="D119" s="131">
         <v>0.05</v>
       </c>
-      <c r="E101" s="131">
+      <c r="E119" s="131">
         <v>0.05</v>
       </c>
-      <c r="F101" s="131">
+      <c r="F119" s="131">
         <v>0.05</v>
       </c>
-      <c r="G101" s="131">
+      <c r="G119" s="131">
         <v>0.05</v>
       </c>
-      <c r="H101" s="131">
+      <c r="H119" s="131">
         <v>0.05</v>
       </c>
-      <c r="I101" s="131">
+      <c r="I119" s="131">
         <v>0.05</v>
       </c>
-      <c r="J101" s="131">
+      <c r="J119" s="131">
         <v>0.1</v>
       </c>
-      <c r="K101" s="131">
+      <c r="K119" s="131">
         <v>0.12</v>
       </c>
-      <c r="L101" s="132">
+      <c r="L119" s="132">
         <v>0.15</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="174"/>
-      <c r="B102" s="122" t="s">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" s="174"/>
+      <c r="B120" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="C102" s="131">
-        <v>0</v>
-      </c>
-      <c r="D102" s="131">
+      <c r="C120" s="131">
+        <v>0</v>
+      </c>
+      <c r="D120" s="131">
         <v>0.1</v>
       </c>
-      <c r="E102" s="131">
+      <c r="E120" s="131">
         <v>0.15</v>
       </c>
-      <c r="F102" s="131">
+      <c r="F120" s="131">
         <v>0.35</v>
       </c>
-      <c r="G102" s="131">
+      <c r="G120" s="131">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H102" s="131">
+      <c r="H120" s="131">
         <v>0.75</v>
       </c>
-      <c r="I102" s="131">
+      <c r="I120" s="131">
         <v>0.85</v>
       </c>
-      <c r="J102" s="131">
+      <c r="J120" s="131">
         <v>0.7</v>
       </c>
-      <c r="K102" s="131">
+      <c r="K120" s="131">
         <v>0.5</v>
       </c>
-      <c r="L102" s="132">
+      <c r="L120" s="132">
         <v>0.35</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="174"/>
-      <c r="B103" s="122" t="s">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="174"/>
+      <c r="B121" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="C103" s="131">
-        <v>0</v>
-      </c>
-      <c r="D103" s="131">
-        <v>0</v>
-      </c>
-      <c r="E103" s="131">
-        <v>0</v>
-      </c>
-      <c r="F103" s="131">
-        <v>0</v>
-      </c>
-      <c r="G103" s="131">
-        <v>0</v>
-      </c>
-      <c r="H103" s="131">
-        <v>0</v>
-      </c>
-      <c r="I103" s="131">
+      <c r="C121" s="131">
+        <v>0</v>
+      </c>
+      <c r="D121" s="131">
+        <v>0</v>
+      </c>
+      <c r="E121" s="131">
+        <v>0</v>
+      </c>
+      <c r="F121" s="131">
+        <v>0</v>
+      </c>
+      <c r="G121" s="131">
+        <v>0</v>
+      </c>
+      <c r="H121" s="131">
+        <v>0</v>
+      </c>
+      <c r="I121" s="131">
         <v>0.05</v>
       </c>
-      <c r="J103" s="131">
+      <c r="J121" s="131">
         <v>0.2</v>
       </c>
-      <c r="K103" s="131">
+      <c r="K121" s="131">
         <v>0.38</v>
       </c>
-      <c r="L103" s="132">
+      <c r="L121" s="132">
         <v>0.5</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="174"/>
-      <c r="B104" s="128" t="s">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" s="174"/>
+      <c r="B122" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="C104" s="131">
-        <v>0</v>
-      </c>
-      <c r="D104" s="131">
-        <v>0</v>
-      </c>
-      <c r="E104" s="131">
-        <v>0</v>
-      </c>
-      <c r="F104" s="131">
-        <v>0</v>
-      </c>
-      <c r="G104" s="131">
-        <v>0</v>
-      </c>
-      <c r="H104" s="131">
-        <v>0</v>
-      </c>
-      <c r="I104" s="131">
-        <v>0</v>
-      </c>
-      <c r="J104" s="131">
-        <v>0</v>
-      </c>
-      <c r="K104" s="131">
-        <v>0</v>
-      </c>
-      <c r="L104" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="175" t="s">
+      <c r="C122" s="131">
+        <v>0</v>
+      </c>
+      <c r="D122" s="131">
+        <v>0</v>
+      </c>
+      <c r="E122" s="131">
+        <v>0</v>
+      </c>
+      <c r="F122" s="131">
+        <v>0</v>
+      </c>
+      <c r="G122" s="131">
+        <v>0</v>
+      </c>
+      <c r="H122" s="131">
+        <v>0</v>
+      </c>
+      <c r="I122" s="131">
+        <v>0</v>
+      </c>
+      <c r="J122" s="131">
+        <v>0</v>
+      </c>
+      <c r="K122" s="131">
+        <v>0</v>
+      </c>
+      <c r="L122" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" s="175" t="s">
         <v>187</v>
       </c>
-      <c r="B105" s="122" t="s">
+      <c r="B123" s="122" t="s">
         <v>184</v>
       </c>
-      <c r="C105" s="131">
+      <c r="C123" s="131">
         <v>0.95</v>
       </c>
-      <c r="D105" s="131">
+      <c r="D123" s="131">
         <v>0.85</v>
       </c>
-      <c r="E105" s="131">
+      <c r="E123" s="131">
         <v>0.8</v>
       </c>
-      <c r="F105" s="131">
+      <c r="F123" s="131">
         <v>0.6</v>
       </c>
-      <c r="G105" s="131">
+      <c r="G123" s="131">
         <v>0.4</v>
       </c>
-      <c r="H105" s="131">
+      <c r="H123" s="131">
         <v>0.2</v>
       </c>
-      <c r="I105" s="131">
+      <c r="I123" s="131">
         <v>0.05</v>
       </c>
-      <c r="J105" s="131">
-        <v>0</v>
-      </c>
-      <c r="K105" s="131">
-        <v>0</v>
-      </c>
-      <c r="L105" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="175"/>
-      <c r="B106" s="122" t="s">
+      <c r="J123" s="131">
+        <v>0</v>
+      </c>
+      <c r="K123" s="131">
+        <v>0</v>
+      </c>
+      <c r="L123" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" s="175"/>
+      <c r="B124" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="C106" s="131">
+      <c r="C124" s="131">
         <v>0.05</v>
       </c>
-      <c r="D106" s="131">
+      <c r="D124" s="131">
         <v>0.05</v>
       </c>
-      <c r="E106" s="131">
+      <c r="E124" s="131">
         <v>0.05</v>
       </c>
-      <c r="F106" s="131">
+      <c r="F124" s="131">
         <v>0.05</v>
       </c>
-      <c r="G106" s="131">
+      <c r="G124" s="131">
         <v>0.05</v>
       </c>
-      <c r="H106" s="131">
+      <c r="H124" s="131">
         <v>0.05</v>
       </c>
-      <c r="I106" s="131">
+      <c r="I124" s="131">
         <v>0.05</v>
       </c>
-      <c r="J106" s="131">
+      <c r="J124" s="131">
         <v>0.05</v>
       </c>
-      <c r="K106" s="131">
+      <c r="K124" s="131">
         <v>0.08</v>
       </c>
-      <c r="L106" s="132">
+      <c r="L124" s="132">
         <v>0.1</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="175"/>
-      <c r="B107" s="122" t="s">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" s="175"/>
+      <c r="B125" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="C107" s="131">
-        <v>0</v>
-      </c>
-      <c r="D107" s="131">
+      <c r="C125" s="131">
+        <v>0</v>
+      </c>
+      <c r="D125" s="131">
         <v>0.1</v>
       </c>
-      <c r="E107" s="131">
+      <c r="E125" s="131">
         <v>0.15</v>
       </c>
-      <c r="F107" s="131">
+      <c r="F125" s="131">
         <v>0.35</v>
       </c>
-      <c r="G107" s="131">
+      <c r="G125" s="131">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H107" s="131">
+      <c r="H125" s="131">
         <v>0.75</v>
       </c>
-      <c r="I107" s="131">
+      <c r="I125" s="131">
         <v>0.85</v>
       </c>
-      <c r="J107" s="131">
+      <c r="J125" s="131">
         <v>0.7</v>
       </c>
-      <c r="K107" s="131">
+      <c r="K125" s="131">
         <v>0.5</v>
       </c>
-      <c r="L107" s="132">
+      <c r="L125" s="132">
         <v>0.35</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="175"/>
-      <c r="B108" s="122" t="s">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" s="175"/>
+      <c r="B126" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="C108" s="131">
-        <v>0</v>
-      </c>
-      <c r="D108" s="131">
-        <v>0</v>
-      </c>
-      <c r="E108" s="131">
-        <v>0</v>
-      </c>
-      <c r="F108" s="131">
-        <v>0</v>
-      </c>
-      <c r="G108" s="131">
-        <v>0</v>
-      </c>
-      <c r="H108" s="131">
-        <v>0</v>
-      </c>
-      <c r="I108" s="131">
+      <c r="C126" s="131">
+        <v>0</v>
+      </c>
+      <c r="D126" s="131">
+        <v>0</v>
+      </c>
+      <c r="E126" s="131">
+        <v>0</v>
+      </c>
+      <c r="F126" s="131">
+        <v>0</v>
+      </c>
+      <c r="G126" s="131">
+        <v>0</v>
+      </c>
+      <c r="H126" s="131">
+        <v>0</v>
+      </c>
+      <c r="I126" s="131">
         <v>0.05</v>
       </c>
-      <c r="J108" s="131">
+      <c r="J126" s="131">
         <v>0.25</v>
       </c>
-      <c r="K108" s="131">
+      <c r="K126" s="131">
         <v>0.42</v>
       </c>
-      <c r="L108" s="132">
+      <c r="L126" s="132">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="175"/>
-      <c r="B109" s="128" t="s">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" s="175"/>
+      <c r="B127" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="C109" s="133">
-        <v>0</v>
-      </c>
-      <c r="D109" s="133">
-        <v>0</v>
-      </c>
-      <c r="E109" s="133">
-        <v>0</v>
-      </c>
-      <c r="F109" s="133">
-        <v>0</v>
-      </c>
-      <c r="G109" s="133">
-        <v>0</v>
-      </c>
-      <c r="H109" s="133">
-        <v>0</v>
-      </c>
-      <c r="I109" s="133">
-        <v>0</v>
-      </c>
-      <c r="J109" s="133">
-        <v>0</v>
-      </c>
-      <c r="K109" s="133">
-        <v>0</v>
-      </c>
-      <c r="L109" s="134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="135" t="s">
+      <c r="C127" s="133">
+        <v>0</v>
+      </c>
+      <c r="D127" s="133">
+        <v>0</v>
+      </c>
+      <c r="E127" s="133">
+        <v>0</v>
+      </c>
+      <c r="F127" s="133">
+        <v>0</v>
+      </c>
+      <c r="G127" s="133">
+        <v>0</v>
+      </c>
+      <c r="H127" s="133">
+        <v>0</v>
+      </c>
+      <c r="I127" s="133">
+        <v>0</v>
+      </c>
+      <c r="J127" s="133">
+        <v>0</v>
+      </c>
+      <c r="K127" s="133">
+        <v>0</v>
+      </c>
+      <c r="L127" s="134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="135" t="s">
         <v>149</v>
       </c>
-      <c r="B113" s="135"/>
-      <c r="C113" s="135"/>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="136" t="s">
+      <c r="B131" s="135"/>
+      <c r="C131" s="135"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="136" t="s">
         <v>150</v>
       </c>
-      <c r="B114" s="137">
+      <c r="B132" s="137">
         <v>4.7200000000000002E-3</v>
       </c>
-      <c r="C114" s="137" t="s">
+      <c r="C132" s="137" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="136" t="s">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="136" t="s">
         <v>152</v>
       </c>
-      <c r="B115" s="137">
-        <v>0</v>
-      </c>
-      <c r="C115" s="137" t="s">
+      <c r="B133" s="137">
+        <v>0</v>
+      </c>
+      <c r="C133" s="137" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="136" t="s">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="136" t="s">
         <v>153</v>
       </c>
-      <c r="B116" s="137">
+      <c r="B134" s="137">
         <v>1.2789999999999999</v>
       </c>
-      <c r="C116" s="137" t="s">
+      <c r="C134" s="137" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="136" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="136" t="s">
         <v>154</v>
       </c>
-      <c r="B117" s="137">
+      <c r="B135" s="137">
         <v>1.711E-2</v>
       </c>
-      <c r="C117" s="137" t="s">
+      <c r="C135" s="137" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="136" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="136" t="s">
         <v>155</v>
       </c>
-      <c r="B118" s="137">
-        <v>0</v>
-      </c>
-      <c r="C118" s="137" t="s">
+      <c r="B136" s="137">
+        <v>0</v>
+      </c>
+      <c r="C136" s="137" t="s">
         <v>151</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="A95:A99"/>
-    <mergeCell ref="A100:A104"/>
-    <mergeCell ref="A105:A109"/>
-    <mergeCell ref="A65:AE65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="A74:AE74"/>
-    <mergeCell ref="A75:A78"/>
+  <mergeCells count="30">
+    <mergeCell ref="A62:AE62"/>
+    <mergeCell ref="A108:A112"/>
+    <mergeCell ref="A113:A117"/>
+    <mergeCell ref="A118:A122"/>
+    <mergeCell ref="A123:A127"/>
+    <mergeCell ref="A67:AE67"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A84:AE84"/>
+    <mergeCell ref="A85:A88"/>
+    <mergeCell ref="A89:A92"/>
+    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A97:A100"/>
     <mergeCell ref="A45:A48"/>
     <mergeCell ref="A49:A52"/>
     <mergeCell ref="A53:A56"/>
@@ -21961,30 +23651,30 @@
       <c r="DE9" s="76"/>
     </row>
     <row r="10" spans="1:109" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="183" t="s">
+      <c r="A10" s="186" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="183"/>
-      <c r="C10" s="183"/>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="183"/>
-      <c r="K10" s="183"/>
-      <c r="L10" s="183"/>
-      <c r="M10" s="183"/>
-      <c r="N10" s="183"/>
-      <c r="O10" s="183"/>
-      <c r="P10" s="183"/>
-      <c r="Q10" s="183"/>
-      <c r="R10" s="183"/>
-      <c r="S10" s="183"/>
-      <c r="T10" s="183"/>
-      <c r="U10" s="183"/>
-      <c r="V10" s="183"/>
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
+      <c r="D10" s="186"/>
+      <c r="E10" s="186"/>
+      <c r="F10" s="186"/>
+      <c r="G10" s="186"/>
+      <c r="H10" s="186"/>
+      <c r="I10" s="186"/>
+      <c r="J10" s="186"/>
+      <c r="K10" s="186"/>
+      <c r="L10" s="186"/>
+      <c r="M10" s="186"/>
+      <c r="N10" s="186"/>
+      <c r="O10" s="186"/>
+      <c r="P10" s="186"/>
+      <c r="Q10" s="186"/>
+      <c r="R10" s="186"/>
+      <c r="S10" s="186"/>
+      <c r="T10" s="186"/>
+      <c r="U10" s="186"/>
+      <c r="V10" s="186"/>
       <c r="DE10" s="76"/>
     </row>
     <row r="11" spans="1:109" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -23014,30 +24704,30 @@
       <c r="DE16" s="83"/>
     </row>
     <row r="17" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A17" s="184" t="s">
+      <c r="A17" s="187" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="184"/>
-      <c r="C17" s="184"/>
-      <c r="D17" s="184"/>
-      <c r="E17" s="184"/>
-      <c r="F17" s="184"/>
-      <c r="G17" s="184"/>
-      <c r="H17" s="184"/>
-      <c r="I17" s="184"/>
-      <c r="J17" s="184"/>
-      <c r="K17" s="184"/>
-      <c r="L17" s="184"/>
-      <c r="M17" s="184"/>
-      <c r="N17" s="184"/>
-      <c r="O17" s="184"/>
-      <c r="P17" s="184"/>
-      <c r="Q17" s="184"/>
-      <c r="R17" s="184"/>
-      <c r="S17" s="184"/>
-      <c r="T17" s="184"/>
-      <c r="U17" s="184"/>
-      <c r="V17" s="184"/>
+      <c r="B17" s="187"/>
+      <c r="C17" s="187"/>
+      <c r="D17" s="187"/>
+      <c r="E17" s="187"/>
+      <c r="F17" s="187"/>
+      <c r="G17" s="187"/>
+      <c r="H17" s="187"/>
+      <c r="I17" s="187"/>
+      <c r="J17" s="187"/>
+      <c r="K17" s="187"/>
+      <c r="L17" s="187"/>
+      <c r="M17" s="187"/>
+      <c r="N17" s="187"/>
+      <c r="O17" s="187"/>
+      <c r="P17" s="187"/>
+      <c r="Q17" s="187"/>
+      <c r="R17" s="187"/>
+      <c r="S17" s="187"/>
+      <c r="T17" s="187"/>
+      <c r="U17" s="187"/>
+      <c r="V17" s="187"/>
       <c r="W17" s="83"/>
       <c r="X17" s="82"/>
       <c r="Y17" s="82"/>
@@ -24264,12 +25954,12 @@
       <c r="DE24" s="83"/>
     </row>
     <row r="25" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A25" s="185" t="s">
+      <c r="A25" s="188" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="185"/>
-      <c r="C25" s="185"/>
-      <c r="D25" s="185"/>
+      <c r="B25" s="188"/>
+      <c r="C25" s="188"/>
+      <c r="D25" s="188"/>
       <c r="E25" s="82"/>
       <c r="F25" s="82"/>
       <c r="G25" s="82"/>
@@ -24492,7 +26182,7 @@
       <c r="DE26" s="83"/>
     </row>
     <row r="27" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A27" s="167" t="s">
+      <c r="A27" s="170" t="s">
         <v>82</v>
       </c>
       <c r="B27" s="64" t="s">
@@ -24611,7 +26301,7 @@
       <c r="DE27" s="83"/>
     </row>
     <row r="28" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A28" s="167"/>
+      <c r="A28" s="170"/>
       <c r="B28" s="64" t="s">
         <v>13</v>
       </c>
@@ -24728,7 +26418,7 @@
       <c r="DE28" s="83"/>
     </row>
     <row r="29" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A29" s="167"/>
+      <c r="A29" s="170"/>
       <c r="B29" s="64" t="s">
         <v>14</v>
       </c>
@@ -24845,7 +26535,7 @@
       <c r="DE29" s="85"/>
     </row>
     <row r="30" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A30" s="167"/>
+      <c r="A30" s="170"/>
       <c r="B30" s="64" t="s">
         <v>83</v>
       </c>
@@ -24962,7 +26652,7 @@
       <c r="DE30" s="85"/>
     </row>
     <row r="31" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A31" s="167" t="s">
+      <c r="A31" s="170" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="64" t="s">
@@ -25081,7 +26771,7 @@
       <c r="DE31" s="85"/>
     </row>
     <row r="32" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A32" s="167"/>
+      <c r="A32" s="170"/>
       <c r="B32" s="64" t="s">
         <v>84</v>
       </c>
@@ -25198,7 +26888,7 @@
       <c r="DE32" s="85"/>
     </row>
     <row r="33" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A33" s="167"/>
+      <c r="A33" s="170"/>
       <c r="B33" s="64" t="s">
         <v>14</v>
       </c>
@@ -25315,7 +27005,7 @@
       <c r="DE33" s="85"/>
     </row>
     <row r="34" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A34" s="167"/>
+      <c r="A34" s="170"/>
       <c r="B34" s="64" t="s">
         <v>83</v>
       </c>
@@ -25432,7 +27122,7 @@
       <c r="DE34" s="85"/>
     </row>
     <row r="35" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A35" s="168" t="s">
+      <c r="A35" s="171" t="s">
         <v>19</v>
       </c>
       <c r="B35" s="64" t="s">
@@ -25551,7 +27241,7 @@
       <c r="DE35" s="85"/>
     </row>
     <row r="36" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A36" s="168"/>
+      <c r="A36" s="171"/>
       <c r="B36" s="64" t="s">
         <v>13</v>
       </c>
@@ -25668,7 +27358,7 @@
       <c r="DE36" s="85"/>
     </row>
     <row r="37" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A37" s="168"/>
+      <c r="A37" s="171"/>
       <c r="B37" s="64" t="s">
         <v>14</v>
       </c>
@@ -25785,7 +27475,7 @@
       <c r="DE37" s="85"/>
     </row>
     <row r="38" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A38" s="168"/>
+      <c r="A38" s="171"/>
       <c r="B38" s="108" t="s">
         <v>83</v>
       </c>
@@ -25902,7 +27592,7 @@
       <c r="DE38" s="85"/>
     </row>
     <row r="39" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A39" s="168" t="s">
+      <c r="A39" s="171" t="s">
         <v>21</v>
       </c>
       <c r="B39" s="64" t="s">
@@ -26020,7 +27710,7 @@
       <c r="DE39" s="85"/>
     </row>
     <row r="40" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A40" s="168"/>
+      <c r="A40" s="171"/>
       <c r="B40" s="64" t="s">
         <v>13</v>
       </c>
@@ -26135,7 +27825,7 @@
       <c r="DE40" s="85"/>
     </row>
     <row r="41" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A41" s="168"/>
+      <c r="A41" s="171"/>
       <c r="B41" s="64" t="s">
         <v>14</v>
       </c>
@@ -26250,7 +27940,7 @@
       <c r="DE41" s="85"/>
     </row>
     <row r="42" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A42" s="168"/>
+      <c r="A42" s="171"/>
       <c r="B42" s="108" t="s">
         <v>83</v>
       </c>
